--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -15144,7 +15144,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118001744</v>
+        <v>118001743</v>
       </c>
       <c r="B142" t="n">
         <v>90660</v>
@@ -15184,10 +15184,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>855545</v>
+        <v>855635</v>
       </c>
       <c r="R142" t="n">
-        <v>7478641</v>
+        <v>7478691</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15228,6 +15228,7 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
@@ -15349,7 +15350,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118001743</v>
+        <v>118001744</v>
       </c>
       <c r="B144" t="n">
         <v>90660</v>
@@ -15389,10 +15390,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>855635</v>
+        <v>855545</v>
       </c>
       <c r="R144" t="n">
-        <v>7478691</v>
+        <v>7478641</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15433,7 +15434,6 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
-      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -15144,10 +15144,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118001743</v>
+        <v>118001745</v>
       </c>
       <c r="B142" t="n">
-        <v>90660</v>
+        <v>90662</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -15184,10 +15184,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>855635</v>
+        <v>855552</v>
       </c>
       <c r="R142" t="n">
-        <v>7478691</v>
+        <v>7478635</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15247,10 +15247,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118001745</v>
+        <v>118001744</v>
       </c>
       <c r="B143" t="n">
-        <v>90660</v>
+        <v>90662</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15287,10 +15287,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>855552</v>
+        <v>855545</v>
       </c>
       <c r="R143" t="n">
-        <v>7478635</v>
+        <v>7478641</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15331,7 +15331,6 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
@@ -15350,10 +15349,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118001744</v>
+        <v>118001743</v>
       </c>
       <c r="B144" t="n">
-        <v>90660</v>
+        <v>90662</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15390,10 +15389,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>855545</v>
+        <v>855635</v>
       </c>
       <c r="R144" t="n">
-        <v>7478641</v>
+        <v>7478691</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15434,6 +15433,7 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -16064,10 +16064,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119677132</v>
+        <v>119677136</v>
       </c>
       <c r="B151" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16080,21 +16080,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16104,10 +16104,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>855595</v>
+        <v>855546</v>
       </c>
       <c r="R151" t="n">
-        <v>7478061</v>
+        <v>7478132</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16166,10 +16166,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119677125</v>
+        <v>119677132</v>
       </c>
       <c r="B152" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16182,21 +16182,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>855570</v>
+        <v>855595</v>
       </c>
       <c r="R152" t="n">
-        <v>7478140</v>
+        <v>7478061</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16268,10 +16268,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119677115</v>
+        <v>119677125</v>
       </c>
       <c r="B153" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16284,21 +16284,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16308,10 +16308,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>855519</v>
+        <v>855570</v>
       </c>
       <c r="R153" t="n">
-        <v>7478115</v>
+        <v>7478140</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16370,10 +16370,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119677136</v>
+        <v>119677115</v>
       </c>
       <c r="B154" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16386,21 +16386,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>855546</v>
+        <v>855519</v>
       </c>
       <c r="R154" t="n">
-        <v>7478132</v>
+        <v>7478115</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -17594,10 +17594,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119677118</v>
+        <v>119677128</v>
       </c>
       <c r="B166" t="n">
-        <v>96856</v>
+        <v>90580</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17606,23 +17606,27 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221944</v>
+        <v>5432</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr"/>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
@@ -17630,10 +17634,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>855491</v>
+        <v>855591</v>
       </c>
       <c r="R166" t="n">
-        <v>7477890</v>
+        <v>7478093</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17674,7 +17678,6 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
@@ -17795,10 +17798,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119677128</v>
+        <v>119677118</v>
       </c>
       <c r="B168" t="n">
-        <v>90580</v>
+        <v>96856</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17807,27 +17810,23 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>5432</v>
+        <v>221944</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -17835,10 +17834,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>855591</v>
+        <v>855491</v>
       </c>
       <c r="R168" t="n">
-        <v>7478093</v>
+        <v>7477890</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17879,6 +17878,7 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
+      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -15452,7 +15452,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119677146</v>
+        <v>119677144</v>
       </c>
       <c r="B145" t="n">
         <v>82305</v>
@@ -15492,10 +15492,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>855547</v>
+        <v>855583</v>
       </c>
       <c r="R145" t="n">
-        <v>7477962</v>
+        <v>7478045</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15554,10 +15554,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119677148</v>
+        <v>119677140</v>
       </c>
       <c r="B146" t="n">
-        <v>77458</v>
+        <v>82305</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15570,21 +15570,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15594,10 +15594,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>855572</v>
+        <v>855582</v>
       </c>
       <c r="R146" t="n">
-        <v>7477969</v>
+        <v>7478091</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15656,10 +15656,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119677124</v>
+        <v>119677113</v>
       </c>
       <c r="B147" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15672,21 +15672,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>855474</v>
+        <v>855429</v>
       </c>
       <c r="R147" t="n">
-        <v>7478024</v>
+        <v>7478011</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15758,7 +15758,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119677144</v>
+        <v>119677133</v>
       </c>
       <c r="B148" t="n">
         <v>82305</v>
@@ -15798,10 +15798,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>855583</v>
+        <v>855497</v>
       </c>
       <c r="R148" t="n">
-        <v>7478045</v>
+        <v>7477946</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15860,7 +15860,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119677134</v>
+        <v>119677145</v>
       </c>
       <c r="B149" t="n">
         <v>82305</v>
@@ -15900,10 +15900,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>855534</v>
+        <v>855589</v>
       </c>
       <c r="R149" t="n">
-        <v>7477979</v>
+        <v>7477997</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119677122</v>
+        <v>119677132</v>
       </c>
       <c r="B150" t="n">
-        <v>90558</v>
+        <v>78526</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15978,21 +15978,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16002,10 +16002,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>855480</v>
+        <v>855595</v>
       </c>
       <c r="R150" t="n">
-        <v>7478054</v>
+        <v>7478061</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16064,10 +16064,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119677136</v>
+        <v>119677115</v>
       </c>
       <c r="B151" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16080,21 +16080,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16104,10 +16104,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>855546</v>
+        <v>855519</v>
       </c>
       <c r="R151" t="n">
-        <v>7478132</v>
+        <v>7478115</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16166,10 +16166,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119677132</v>
+        <v>119677137</v>
       </c>
       <c r="B152" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16182,21 +16182,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>855595</v>
+        <v>855557</v>
       </c>
       <c r="R152" t="n">
-        <v>7478061</v>
+        <v>7478143</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16268,10 +16268,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119677125</v>
+        <v>119677138</v>
       </c>
       <c r="B153" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16284,21 +16284,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16308,10 +16308,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>855570</v>
+        <v>855571</v>
       </c>
       <c r="R153" t="n">
-        <v>7478140</v>
+        <v>7478136</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16370,10 +16370,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119677115</v>
+        <v>119677123</v>
       </c>
       <c r="B154" t="n">
-        <v>57326</v>
+        <v>90580</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16386,21 +16386,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>855519</v>
+        <v>855409</v>
       </c>
       <c r="R154" t="n">
-        <v>7478115</v>
+        <v>7478024</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16472,10 +16472,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119677107</v>
+        <v>119677118</v>
       </c>
       <c r="B155" t="n">
-        <v>90724</v>
+        <v>96856</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16484,27 +16484,23 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1588</v>
+        <v>221944</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -16512,10 +16508,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>855583</v>
+        <v>855491</v>
       </c>
       <c r="R155" t="n">
-        <v>7478066</v>
+        <v>7477890</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16556,6 +16552,7 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
+      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -16574,10 +16571,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119677135</v>
+        <v>119677107</v>
       </c>
       <c r="B156" t="n">
-        <v>82305</v>
+        <v>90724</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16590,21 +16587,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1312</v>
+        <v>1588</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16614,10 +16611,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>855530</v>
+        <v>855583</v>
       </c>
       <c r="R156" t="n">
-        <v>7478027</v>
+        <v>7478066</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16676,10 +16673,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119677116</v>
+        <v>119677109</v>
       </c>
       <c r="B157" t="n">
-        <v>90334</v>
+        <v>90527</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16692,21 +16689,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16716,10 +16713,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>855497</v>
+        <v>855492</v>
       </c>
       <c r="R157" t="n">
-        <v>7477896</v>
+        <v>7477928</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16778,10 +16775,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119677121</v>
+        <v>119677117</v>
       </c>
       <c r="B158" t="n">
-        <v>90558</v>
+        <v>90846</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16794,21 +16791,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1108</v>
+        <v>658</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16818,10 +16815,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>855458</v>
+        <v>855412</v>
       </c>
       <c r="R158" t="n">
-        <v>7478069</v>
+        <v>7478048</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16880,10 +16877,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119677141</v>
+        <v>119677124</v>
       </c>
       <c r="B159" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16896,21 +16893,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16920,10 +16917,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>855579</v>
+        <v>855474</v>
       </c>
       <c r="R159" t="n">
-        <v>7478063</v>
+        <v>7478024</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16982,10 +16979,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119677113</v>
+        <v>119677110</v>
       </c>
       <c r="B160" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16994,25 +16991,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17022,10 +17019,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>855429</v>
+        <v>855517</v>
       </c>
       <c r="R160" t="n">
-        <v>7478011</v>
+        <v>7477955</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17084,10 +17081,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119677108</v>
+        <v>119677125</v>
       </c>
       <c r="B161" t="n">
-        <v>58022</v>
+        <v>90580</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17100,21 +17097,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>103056</v>
+        <v>5432</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17124,10 +17121,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>855446</v>
+        <v>855570</v>
       </c>
       <c r="R161" t="n">
-        <v>7478072</v>
+        <v>7478140</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17186,7 +17183,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119677142</v>
+        <v>119677141</v>
       </c>
       <c r="B162" t="n">
         <v>82305</v>
@@ -17226,10 +17223,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>855580</v>
+        <v>855579</v>
       </c>
       <c r="R162" t="n">
-        <v>7478058</v>
+        <v>7478063</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17288,10 +17285,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119677123</v>
+        <v>119677142</v>
       </c>
       <c r="B163" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17304,21 +17301,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17328,10 +17325,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>855409</v>
+        <v>855580</v>
       </c>
       <c r="R163" t="n">
-        <v>7478024</v>
+        <v>7478058</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17390,10 +17387,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119677109</v>
+        <v>119677143</v>
       </c>
       <c r="B164" t="n">
-        <v>90527</v>
+        <v>82305</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17402,25 +17399,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17430,10 +17427,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>855492</v>
+        <v>855583</v>
       </c>
       <c r="R164" t="n">
-        <v>7477928</v>
+        <v>7478050</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17492,10 +17489,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119677110</v>
+        <v>119677128</v>
       </c>
       <c r="B165" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17504,25 +17501,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17532,10 +17529,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>855517</v>
+        <v>855591</v>
       </c>
       <c r="R165" t="n">
-        <v>7477955</v>
+        <v>7478093</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17594,10 +17591,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119677128</v>
+        <v>119677121</v>
       </c>
       <c r="B166" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17610,21 +17607,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17634,10 +17631,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>855591</v>
+        <v>855458</v>
       </c>
       <c r="R166" t="n">
-        <v>7478093</v>
+        <v>7478069</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17696,7 +17693,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119677119</v>
+        <v>119677122</v>
       </c>
       <c r="B167" t="n">
         <v>90558</v>
@@ -17736,10 +17733,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>855500</v>
+        <v>855480</v>
       </c>
       <c r="R167" t="n">
-        <v>7478086</v>
+        <v>7478054</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17798,10 +17795,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119677118</v>
+        <v>119677134</v>
       </c>
       <c r="B168" t="n">
-        <v>96856</v>
+        <v>82305</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17810,23 +17807,27 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221944</v>
+        <v>1312</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr"/>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
       <c r="I168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
@@ -17834,10 +17835,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>855491</v>
+        <v>855534</v>
       </c>
       <c r="R168" t="n">
-        <v>7477890</v>
+        <v>7477979</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17878,7 +17879,6 @@
       <c r="AE168" t="b">
         <v>0</v>
       </c>
-      <c r="AF168" t="inlineStr"/>
       <c r="AG168" t="b">
         <v>0</v>
       </c>
@@ -17897,7 +17897,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119677145</v>
+        <v>119677135</v>
       </c>
       <c r="B169" t="n">
         <v>82305</v>
@@ -17937,10 +17937,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>855589</v>
+        <v>855530</v>
       </c>
       <c r="R169" t="n">
-        <v>7477997</v>
+        <v>7478027</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17999,10 +17999,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119677127</v>
+        <v>119677104</v>
       </c>
       <c r="B170" t="n">
-        <v>90580</v>
+        <v>104994</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18011,25 +18011,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18039,10 +18039,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>855584</v>
+        <v>855591</v>
       </c>
       <c r="R170" t="n">
-        <v>7478103</v>
+        <v>7478061</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18101,10 +18101,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119677111</v>
+        <v>119677114</v>
       </c>
       <c r="B171" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18113,25 +18113,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18141,10 +18141,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>855540</v>
+        <v>855595</v>
       </c>
       <c r="R171" t="n">
-        <v>7478006</v>
+        <v>7478114</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18203,10 +18203,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119677117</v>
+        <v>119677136</v>
       </c>
       <c r="B172" t="n">
-        <v>90846</v>
+        <v>82305</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18219,21 +18219,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18243,10 +18243,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>855412</v>
+        <v>855546</v>
       </c>
       <c r="R172" t="n">
-        <v>7478048</v>
+        <v>7478132</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18305,10 +18305,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119677137</v>
+        <v>119677127</v>
       </c>
       <c r="B173" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18321,21 +18321,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18345,10 +18345,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>855557</v>
+        <v>855584</v>
       </c>
       <c r="R173" t="n">
-        <v>7478143</v>
+        <v>7478103</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18407,10 +18407,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119677133</v>
+        <v>119677116</v>
       </c>
       <c r="B174" t="n">
-        <v>82305</v>
+        <v>90334</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18419,25 +18419,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1312</v>
+        <v>3215</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18450,7 +18450,7 @@
         <v>855497</v>
       </c>
       <c r="R174" t="n">
-        <v>7477946</v>
+        <v>7477896</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18509,10 +18509,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119677114</v>
+        <v>119677108</v>
       </c>
       <c r="B175" t="n">
-        <v>90562</v>
+        <v>58022</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>1202</v>
+        <v>103056</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>855595</v>
+        <v>855446</v>
       </c>
       <c r="R175" t="n">
-        <v>7478114</v>
+        <v>7478072</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18611,10 +18611,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119677140</v>
+        <v>119677131</v>
       </c>
       <c r="B176" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18627,21 +18627,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18651,10 +18651,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>855582</v>
+        <v>855581</v>
       </c>
       <c r="R176" t="n">
-        <v>7478091</v>
+        <v>7478131</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18713,10 +18713,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119677143</v>
+        <v>119677148</v>
       </c>
       <c r="B177" t="n">
-        <v>82305</v>
+        <v>77458</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18729,21 +18729,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18753,10 +18753,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>855583</v>
+        <v>855572</v>
       </c>
       <c r="R177" t="n">
-        <v>7478050</v>
+        <v>7477969</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18815,10 +18815,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119677131</v>
+        <v>119677106</v>
       </c>
       <c r="B178" t="n">
-        <v>78526</v>
+        <v>104994</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18827,25 +18827,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18855,10 +18855,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>855581</v>
+        <v>855590</v>
       </c>
       <c r="R178" t="n">
-        <v>7478131</v>
+        <v>7478066</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18917,10 +18917,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119677106</v>
+        <v>119677119</v>
       </c>
       <c r="B179" t="n">
-        <v>104994</v>
+        <v>90558</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18929,25 +18929,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>221725</v>
+        <v>1108</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18957,10 +18957,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>855590</v>
+        <v>855500</v>
       </c>
       <c r="R179" t="n">
-        <v>7478066</v>
+        <v>7478086</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19019,10 +19019,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119677104</v>
+        <v>119677139</v>
       </c>
       <c r="B180" t="n">
-        <v>104994</v>
+        <v>82305</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19031,25 +19031,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>855591</v>
+        <v>855582</v>
       </c>
       <c r="R180" t="n">
-        <v>7478061</v>
+        <v>7478106</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19121,10 +19121,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119677139</v>
+        <v>119677111</v>
       </c>
       <c r="B181" t="n">
-        <v>82305</v>
+        <v>90527</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19133,25 +19133,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19161,10 +19161,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>855582</v>
+        <v>855540</v>
       </c>
       <c r="R181" t="n">
-        <v>7478106</v>
+        <v>7478006</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19223,7 +19223,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119677138</v>
+        <v>119677146</v>
       </c>
       <c r="B182" t="n">
         <v>82305</v>
@@ -19263,10 +19263,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>855571</v>
+        <v>855547</v>
       </c>
       <c r="R182" t="n">
-        <v>7478136</v>
+        <v>7477962</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -16472,10 +16472,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119677118</v>
+        <v>119677107</v>
       </c>
       <c r="B155" t="n">
-        <v>96856</v>
+        <v>90724</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16484,23 +16484,27 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>221944</v>
+        <v>1588</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
+          <t>Trichaptum laricinum</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
       <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
@@ -16508,10 +16512,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>855491</v>
+        <v>855583</v>
       </c>
       <c r="R155" t="n">
-        <v>7477890</v>
+        <v>7478066</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16552,7 +16556,6 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
@@ -16571,10 +16574,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119677107</v>
+        <v>119677118</v>
       </c>
       <c r="B156" t="n">
-        <v>90724</v>
+        <v>96856</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16583,27 +16586,23 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1588</v>
+        <v>221944</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -16611,10 +16610,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>855583</v>
+        <v>855491</v>
       </c>
       <c r="R156" t="n">
-        <v>7478066</v>
+        <v>7477890</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16655,6 +16654,7 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -15452,10 +15452,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119677144</v>
+        <v>119677123</v>
       </c>
       <c r="B145" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15468,21 +15468,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15492,10 +15492,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>855583</v>
+        <v>855409</v>
       </c>
       <c r="R145" t="n">
-        <v>7478045</v>
+        <v>7478024</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15554,10 +15554,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119677140</v>
+        <v>119677114</v>
       </c>
       <c r="B146" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15570,21 +15570,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15594,10 +15594,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>855582</v>
+        <v>855595</v>
       </c>
       <c r="R146" t="n">
-        <v>7478091</v>
+        <v>7478114</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15656,10 +15656,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119677113</v>
+        <v>119677111</v>
       </c>
       <c r="B147" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15668,25 +15668,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>855429</v>
+        <v>855540</v>
       </c>
       <c r="R147" t="n">
-        <v>7478011</v>
+        <v>7478006</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15758,7 +15758,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119677133</v>
+        <v>119677140</v>
       </c>
       <c r="B148" t="n">
         <v>82305</v>
@@ -15798,10 +15798,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>855497</v>
+        <v>855582</v>
       </c>
       <c r="R148" t="n">
-        <v>7477946</v>
+        <v>7478091</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15860,10 +15860,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119677145</v>
+        <v>119677115</v>
       </c>
       <c r="B149" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15876,21 +15876,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15900,10 +15900,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>855589</v>
+        <v>855519</v>
       </c>
       <c r="R149" t="n">
-        <v>7477997</v>
+        <v>7478115</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119677132</v>
+        <v>119677107</v>
       </c>
       <c r="B150" t="n">
-        <v>78526</v>
+        <v>90724</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15978,21 +15978,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>1588</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16002,10 +16002,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>855595</v>
+        <v>855583</v>
       </c>
       <c r="R150" t="n">
-        <v>7478061</v>
+        <v>7478066</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16064,10 +16064,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119677115</v>
+        <v>119677122</v>
       </c>
       <c r="B151" t="n">
-        <v>57326</v>
+        <v>90558</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -16080,21 +16080,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16104,10 +16104,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>855519</v>
+        <v>855480</v>
       </c>
       <c r="R151" t="n">
-        <v>7478115</v>
+        <v>7478054</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16166,10 +16166,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119677137</v>
+        <v>119677132</v>
       </c>
       <c r="B152" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16182,21 +16182,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>855557</v>
+        <v>855595</v>
       </c>
       <c r="R152" t="n">
-        <v>7478143</v>
+        <v>7478061</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16268,7 +16268,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119677138</v>
+        <v>119677133</v>
       </c>
       <c r="B153" t="n">
         <v>82305</v>
@@ -16308,10 +16308,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>855571</v>
+        <v>855497</v>
       </c>
       <c r="R153" t="n">
-        <v>7478136</v>
+        <v>7477946</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16370,10 +16370,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119677123</v>
+        <v>119677135</v>
       </c>
       <c r="B154" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16386,21 +16386,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>855409</v>
+        <v>855530</v>
       </c>
       <c r="R154" t="n">
-        <v>7478024</v>
+        <v>7478027</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16472,10 +16472,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119677107</v>
+        <v>119677110</v>
       </c>
       <c r="B155" t="n">
-        <v>90724</v>
+        <v>90527</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16484,25 +16484,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16512,10 +16512,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>855583</v>
+        <v>855517</v>
       </c>
       <c r="R155" t="n">
-        <v>7478066</v>
+        <v>7477955</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16574,10 +16574,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119677118</v>
+        <v>119677108</v>
       </c>
       <c r="B156" t="n">
-        <v>96856</v>
+        <v>58022</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16586,23 +16586,27 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>221944</v>
+        <v>103056</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr"/>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
       <c r="I156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
@@ -16610,10 +16614,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>855491</v>
+        <v>855446</v>
       </c>
       <c r="R156" t="n">
-        <v>7477890</v>
+        <v>7478072</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16654,7 +16658,6 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -16673,10 +16676,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119677109</v>
+        <v>119677134</v>
       </c>
       <c r="B157" t="n">
-        <v>90527</v>
+        <v>82305</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16685,25 +16688,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16713,10 +16716,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>855492</v>
+        <v>855534</v>
       </c>
       <c r="R157" t="n">
-        <v>7477928</v>
+        <v>7477979</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16775,10 +16778,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119677117</v>
+        <v>119677125</v>
       </c>
       <c r="B158" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16791,21 +16794,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16815,10 +16818,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>855412</v>
+        <v>855570</v>
       </c>
       <c r="R158" t="n">
-        <v>7478048</v>
+        <v>7478140</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16877,10 +16880,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119677124</v>
+        <v>119677119</v>
       </c>
       <c r="B159" t="n">
-        <v>90580</v>
+        <v>90558</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16893,21 +16896,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16917,10 +16920,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>855474</v>
+        <v>855500</v>
       </c>
       <c r="R159" t="n">
-        <v>7478024</v>
+        <v>7478086</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16979,10 +16982,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119677110</v>
+        <v>119677106</v>
       </c>
       <c r="B160" t="n">
-        <v>90527</v>
+        <v>104994</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16995,21 +16998,21 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5447</v>
+        <v>221725</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17019,10 +17022,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>855517</v>
+        <v>855590</v>
       </c>
       <c r="R160" t="n">
-        <v>7477955</v>
+        <v>7478066</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17081,10 +17084,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119677125</v>
+        <v>119677104</v>
       </c>
       <c r="B161" t="n">
-        <v>90580</v>
+        <v>104994</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17093,25 +17096,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -17121,10 +17124,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>855570</v>
+        <v>855591</v>
       </c>
       <c r="R161" t="n">
-        <v>7478140</v>
+        <v>7478061</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17183,7 +17186,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119677141</v>
+        <v>119677137</v>
       </c>
       <c r="B162" t="n">
         <v>82305</v>
@@ -17223,10 +17226,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>855579</v>
+        <v>855557</v>
       </c>
       <c r="R162" t="n">
-        <v>7478063</v>
+        <v>7478143</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17285,10 +17288,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119677142</v>
+        <v>119677109</v>
       </c>
       <c r="B163" t="n">
-        <v>82305</v>
+        <v>90527</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17297,25 +17300,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17325,10 +17328,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>855580</v>
+        <v>855492</v>
       </c>
       <c r="R163" t="n">
-        <v>7478058</v>
+        <v>7477928</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17387,7 +17390,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119677143</v>
+        <v>119677144</v>
       </c>
       <c r="B164" t="n">
         <v>82305</v>
@@ -17430,7 +17433,7 @@
         <v>855583</v>
       </c>
       <c r="R164" t="n">
-        <v>7478050</v>
+        <v>7478045</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17489,10 +17492,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119677128</v>
+        <v>119677113</v>
       </c>
       <c r="B165" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17505,21 +17508,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17529,10 +17532,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>855591</v>
+        <v>855429</v>
       </c>
       <c r="R165" t="n">
-        <v>7478093</v>
+        <v>7478011</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17591,10 +17594,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119677121</v>
+        <v>119677128</v>
       </c>
       <c r="B166" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17607,21 +17610,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17631,10 +17634,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>855458</v>
+        <v>855591</v>
       </c>
       <c r="R166" t="n">
-        <v>7478069</v>
+        <v>7478093</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17693,10 +17696,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119677122</v>
+        <v>119677143</v>
       </c>
       <c r="B167" t="n">
-        <v>90558</v>
+        <v>82305</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17709,21 +17712,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17733,10 +17736,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>855480</v>
+        <v>855583</v>
       </c>
       <c r="R167" t="n">
-        <v>7478054</v>
+        <v>7478050</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17795,7 +17798,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119677134</v>
+        <v>119677142</v>
       </c>
       <c r="B168" t="n">
         <v>82305</v>
@@ -17835,10 +17838,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>855534</v>
+        <v>855580</v>
       </c>
       <c r="R168" t="n">
-        <v>7477979</v>
+        <v>7478058</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17897,7 +17900,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119677135</v>
+        <v>119677136</v>
       </c>
       <c r="B169" t="n">
         <v>82305</v>
@@ -17937,10 +17940,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>855530</v>
+        <v>855546</v>
       </c>
       <c r="R169" t="n">
-        <v>7478027</v>
+        <v>7478132</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17999,10 +18002,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119677104</v>
+        <v>119677116</v>
       </c>
       <c r="B170" t="n">
-        <v>104994</v>
+        <v>90334</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18015,21 +18018,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>221725</v>
+        <v>3215</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18039,10 +18042,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>855591</v>
+        <v>855497</v>
       </c>
       <c r="R170" t="n">
-        <v>7478061</v>
+        <v>7477896</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18101,10 +18104,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119677114</v>
+        <v>119677118</v>
       </c>
       <c r="B171" t="n">
-        <v>90562</v>
+        <v>96856</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18113,27 +18116,23 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1202</v>
+        <v>221944</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
@@ -18141,10 +18140,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>855595</v>
+        <v>855491</v>
       </c>
       <c r="R171" t="n">
-        <v>7478114</v>
+        <v>7477890</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18185,6 +18184,7 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -18203,10 +18203,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119677136</v>
+        <v>119677131</v>
       </c>
       <c r="B172" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18219,21 +18219,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18243,10 +18243,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>855546</v>
+        <v>855581</v>
       </c>
       <c r="R172" t="n">
-        <v>7478132</v>
+        <v>7478131</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18305,10 +18305,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119677127</v>
+        <v>119677117</v>
       </c>
       <c r="B173" t="n">
-        <v>90580</v>
+        <v>90846</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18321,21 +18321,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18345,10 +18345,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>855584</v>
+        <v>855412</v>
       </c>
       <c r="R173" t="n">
-        <v>7478103</v>
+        <v>7478048</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18407,10 +18407,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119677116</v>
+        <v>119677127</v>
       </c>
       <c r="B174" t="n">
-        <v>90334</v>
+        <v>90580</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18419,25 +18419,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>3215</v>
+        <v>5432</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18447,10 +18447,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>855497</v>
+        <v>855584</v>
       </c>
       <c r="R174" t="n">
-        <v>7477896</v>
+        <v>7478103</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18509,10 +18509,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119677108</v>
+        <v>119677124</v>
       </c>
       <c r="B175" t="n">
-        <v>58022</v>
+        <v>90580</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18525,21 +18525,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>103056</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>855446</v>
+        <v>855474</v>
       </c>
       <c r="R175" t="n">
-        <v>7478072</v>
+        <v>7478024</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18611,10 +18611,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119677131</v>
+        <v>119677146</v>
       </c>
       <c r="B176" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18627,21 +18627,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18651,10 +18651,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>855581</v>
+        <v>855547</v>
       </c>
       <c r="R176" t="n">
-        <v>7478131</v>
+        <v>7477962</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18713,10 +18713,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119677148</v>
+        <v>119677145</v>
       </c>
       <c r="B177" t="n">
-        <v>77458</v>
+        <v>82305</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18729,21 +18729,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18753,10 +18753,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>855572</v>
+        <v>855589</v>
       </c>
       <c r="R177" t="n">
-        <v>7477969</v>
+        <v>7477997</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18815,10 +18815,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119677106</v>
+        <v>119677138</v>
       </c>
       <c r="B178" t="n">
-        <v>104994</v>
+        <v>82305</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18827,25 +18827,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18855,10 +18855,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>855590</v>
+        <v>855571</v>
       </c>
       <c r="R178" t="n">
-        <v>7478066</v>
+        <v>7478136</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18917,10 +18917,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119677119</v>
+        <v>119677141</v>
       </c>
       <c r="B179" t="n">
-        <v>90558</v>
+        <v>82305</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18933,21 +18933,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18957,10 +18957,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>855500</v>
+        <v>855579</v>
       </c>
       <c r="R179" t="n">
-        <v>7478086</v>
+        <v>7478063</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19019,10 +19019,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119677139</v>
+        <v>119677121</v>
       </c>
       <c r="B180" t="n">
-        <v>82305</v>
+        <v>90558</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19035,21 +19035,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>855582</v>
+        <v>855458</v>
       </c>
       <c r="R180" t="n">
-        <v>7478106</v>
+        <v>7478069</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19121,10 +19121,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119677111</v>
+        <v>119677139</v>
       </c>
       <c r="B181" t="n">
-        <v>90527</v>
+        <v>82305</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -19133,25 +19133,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -19161,10 +19161,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>855540</v>
+        <v>855582</v>
       </c>
       <c r="R181" t="n">
-        <v>7478006</v>
+        <v>7478106</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19223,10 +19223,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119677146</v>
+        <v>119677148</v>
       </c>
       <c r="B182" t="n">
-        <v>82305</v>
+        <v>77458</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19239,21 +19239,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19263,10 +19263,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>855547</v>
+        <v>855572</v>
       </c>
       <c r="R182" t="n">
-        <v>7477962</v>
+        <v>7477969</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -15758,10 +15758,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119677140</v>
+        <v>119677115</v>
       </c>
       <c r="B148" t="n">
-        <v>82305</v>
+        <v>57326</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15774,21 +15774,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15798,10 +15798,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>855582</v>
+        <v>855519</v>
       </c>
       <c r="R148" t="n">
-        <v>7478091</v>
+        <v>7478115</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15860,10 +15860,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119677115</v>
+        <v>119677140</v>
       </c>
       <c r="B149" t="n">
-        <v>57326</v>
+        <v>82305</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15876,21 +15876,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15900,10 +15900,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>855519</v>
+        <v>855582</v>
       </c>
       <c r="R149" t="n">
-        <v>7478115</v>
+        <v>7478091</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16676,10 +16676,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119677134</v>
+        <v>119677125</v>
       </c>
       <c r="B157" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16692,21 +16692,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16716,10 +16716,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>855534</v>
+        <v>855570</v>
       </c>
       <c r="R157" t="n">
-        <v>7477979</v>
+        <v>7478140</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16778,10 +16778,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119677125</v>
+        <v>119677134</v>
       </c>
       <c r="B158" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16794,21 +16794,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16818,10 +16818,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>855570</v>
+        <v>855534</v>
       </c>
       <c r="R158" t="n">
-        <v>7478140</v>
+        <v>7477979</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -15452,10 +15452,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119677123</v>
+        <v>119677106</v>
       </c>
       <c r="B145" t="n">
-        <v>90580</v>
+        <v>104994</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15464,25 +15464,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15492,10 +15492,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>855409</v>
+        <v>855590</v>
       </c>
       <c r="R145" t="n">
-        <v>7478024</v>
+        <v>7478066</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15554,10 +15554,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119677114</v>
+        <v>119677121</v>
       </c>
       <c r="B146" t="n">
-        <v>90562</v>
+        <v>90558</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15570,21 +15570,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15594,10 +15594,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>855595</v>
+        <v>855458</v>
       </c>
       <c r="R146" t="n">
-        <v>7478114</v>
+        <v>7478069</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15656,10 +15656,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119677111</v>
+        <v>119677116</v>
       </c>
       <c r="B147" t="n">
-        <v>90527</v>
+        <v>90334</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15672,21 +15672,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5447</v>
+        <v>3215</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>855540</v>
+        <v>855497</v>
       </c>
       <c r="R147" t="n">
-        <v>7478006</v>
+        <v>7477896</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15758,10 +15758,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119677115</v>
+        <v>119677145</v>
       </c>
       <c r="B148" t="n">
-        <v>57326</v>
+        <v>82305</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15774,21 +15774,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15798,10 +15798,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>855519</v>
+        <v>855589</v>
       </c>
       <c r="R148" t="n">
-        <v>7478115</v>
+        <v>7477997</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15860,7 +15860,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119677140</v>
+        <v>119677143</v>
       </c>
       <c r="B149" t="n">
         <v>82305</v>
@@ -15900,10 +15900,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>855582</v>
+        <v>855583</v>
       </c>
       <c r="R149" t="n">
-        <v>7478091</v>
+        <v>7478050</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15962,10 +15962,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119677107</v>
+        <v>119677114</v>
       </c>
       <c r="B150" t="n">
-        <v>90724</v>
+        <v>90562</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15978,21 +15978,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1588</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16002,10 +16002,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>855583</v>
+        <v>855595</v>
       </c>
       <c r="R150" t="n">
-        <v>7478066</v>
+        <v>7478114</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16064,7 +16064,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119677122</v>
+        <v>119677119</v>
       </c>
       <c r="B151" t="n">
         <v>90558</v>
@@ -16104,10 +16104,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>855480</v>
+        <v>855500</v>
       </c>
       <c r="R151" t="n">
-        <v>7478054</v>
+        <v>7478086</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16166,10 +16166,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119677132</v>
+        <v>119677146</v>
       </c>
       <c r="B152" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
@@ -16182,21 +16182,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16206,10 +16206,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>855595</v>
+        <v>855547</v>
       </c>
       <c r="R152" t="n">
-        <v>7478061</v>
+        <v>7477962</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16268,7 +16268,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119677133</v>
+        <v>119677137</v>
       </c>
       <c r="B153" t="n">
         <v>82305</v>
@@ -16308,10 +16308,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>855497</v>
+        <v>855557</v>
       </c>
       <c r="R153" t="n">
-        <v>7477946</v>
+        <v>7478143</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16370,10 +16370,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119677135</v>
+        <v>119677131</v>
       </c>
       <c r="B154" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16386,21 +16386,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16410,10 +16410,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>855530</v>
+        <v>855581</v>
       </c>
       <c r="R154" t="n">
-        <v>7478027</v>
+        <v>7478131</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16472,10 +16472,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119677110</v>
+        <v>119677108</v>
       </c>
       <c r="B155" t="n">
-        <v>90527</v>
+        <v>58022</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16484,25 +16484,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>5447</v>
+        <v>103056</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16512,10 +16512,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>855517</v>
+        <v>855446</v>
       </c>
       <c r="R155" t="n">
-        <v>7477955</v>
+        <v>7478072</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16574,10 +16574,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119677108</v>
+        <v>119677111</v>
       </c>
       <c r="B156" t="n">
-        <v>58022</v>
+        <v>90527</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16586,25 +16586,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>103056</v>
+        <v>5447</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16614,10 +16614,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>855446</v>
+        <v>855540</v>
       </c>
       <c r="R156" t="n">
-        <v>7478072</v>
+        <v>7478006</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16676,10 +16676,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119677125</v>
+        <v>119677134</v>
       </c>
       <c r="B157" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16692,21 +16692,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16716,10 +16716,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>855570</v>
+        <v>855534</v>
       </c>
       <c r="R157" t="n">
-        <v>7478140</v>
+        <v>7477979</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16778,10 +16778,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119677134</v>
+        <v>119677125</v>
       </c>
       <c r="B158" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16794,21 +16794,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16818,10 +16818,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>855534</v>
+        <v>855570</v>
       </c>
       <c r="R158" t="n">
-        <v>7477979</v>
+        <v>7478140</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16880,10 +16880,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119677119</v>
+        <v>119677109</v>
       </c>
       <c r="B159" t="n">
-        <v>90558</v>
+        <v>90527</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16892,25 +16892,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16920,10 +16920,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>855500</v>
+        <v>855492</v>
       </c>
       <c r="R159" t="n">
-        <v>7478086</v>
+        <v>7477928</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16982,10 +16982,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119677106</v>
+        <v>119677140</v>
       </c>
       <c r="B160" t="n">
-        <v>104994</v>
+        <v>82305</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16994,25 +16994,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>221725</v>
+        <v>1312</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -17022,10 +17022,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>855590</v>
+        <v>855582</v>
       </c>
       <c r="R160" t="n">
-        <v>7478066</v>
+        <v>7478091</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -17084,10 +17084,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119677104</v>
+        <v>119677118</v>
       </c>
       <c r="B161" t="n">
-        <v>104994</v>
+        <v>96856</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -17100,23 +17100,19 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>221725</v>
+        <v>221944</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -17124,10 +17120,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>855591</v>
+        <v>855491</v>
       </c>
       <c r="R161" t="n">
-        <v>7478061</v>
+        <v>7477890</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17168,6 +17164,7 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -17186,7 +17183,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119677137</v>
+        <v>119677136</v>
       </c>
       <c r="B162" t="n">
         <v>82305</v>
@@ -17226,10 +17223,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>855557</v>
+        <v>855546</v>
       </c>
       <c r="R162" t="n">
-        <v>7478143</v>
+        <v>7478132</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17288,10 +17285,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119677109</v>
+        <v>119677142</v>
       </c>
       <c r="B163" t="n">
-        <v>90527</v>
+        <v>82305</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17300,25 +17297,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17328,10 +17325,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>855492</v>
+        <v>855580</v>
       </c>
       <c r="R163" t="n">
-        <v>7477928</v>
+        <v>7478058</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17390,10 +17387,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119677144</v>
+        <v>119677122</v>
       </c>
       <c r="B164" t="n">
-        <v>82305</v>
+        <v>90558</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17406,21 +17403,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17430,10 +17427,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>855583</v>
+        <v>855480</v>
       </c>
       <c r="R164" t="n">
-        <v>7478045</v>
+        <v>7478054</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17492,10 +17489,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119677113</v>
+        <v>119677141</v>
       </c>
       <c r="B165" t="n">
-        <v>90562</v>
+        <v>82305</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17508,21 +17505,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17532,10 +17529,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>855429</v>
+        <v>855579</v>
       </c>
       <c r="R165" t="n">
-        <v>7478011</v>
+        <v>7478063</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17594,10 +17591,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119677128</v>
+        <v>119677107</v>
       </c>
       <c r="B166" t="n">
-        <v>90580</v>
+        <v>90724</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17610,21 +17607,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17634,10 +17631,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>855591</v>
+        <v>855583</v>
       </c>
       <c r="R166" t="n">
-        <v>7478093</v>
+        <v>7478066</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17696,10 +17693,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119677143</v>
+        <v>119677113</v>
       </c>
       <c r="B167" t="n">
-        <v>82305</v>
+        <v>90562</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17712,21 +17709,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17736,10 +17733,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>855583</v>
+        <v>855429</v>
       </c>
       <c r="R167" t="n">
-        <v>7478050</v>
+        <v>7478011</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17798,7 +17795,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119677142</v>
+        <v>119677138</v>
       </c>
       <c r="B168" t="n">
         <v>82305</v>
@@ -17838,10 +17835,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>855580</v>
+        <v>855571</v>
       </c>
       <c r="R168" t="n">
-        <v>7478058</v>
+        <v>7478136</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17900,10 +17897,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119677136</v>
+        <v>119677128</v>
       </c>
       <c r="B169" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17916,21 +17913,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17940,10 +17937,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>855546</v>
+        <v>855591</v>
       </c>
       <c r="R169" t="n">
-        <v>7478132</v>
+        <v>7478093</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18002,10 +17999,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119677116</v>
+        <v>119677110</v>
       </c>
       <c r="B170" t="n">
-        <v>90334</v>
+        <v>90527</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18018,21 +18015,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18042,10 +18039,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>855497</v>
+        <v>855517</v>
       </c>
       <c r="R170" t="n">
-        <v>7477896</v>
+        <v>7477955</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18104,10 +18101,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119677118</v>
+        <v>119677148</v>
       </c>
       <c r="B171" t="n">
-        <v>96856</v>
+        <v>77458</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18116,23 +18113,27 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>221944</v>
+        <v>6487</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr"/>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
@@ -18140,10 +18141,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>855491</v>
+        <v>855572</v>
       </c>
       <c r="R171" t="n">
-        <v>7477890</v>
+        <v>7477969</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18184,7 +18185,6 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
-      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
       </c>
@@ -18203,10 +18203,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119677131</v>
+        <v>119677133</v>
       </c>
       <c r="B172" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18219,21 +18219,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18243,10 +18243,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>855581</v>
+        <v>855497</v>
       </c>
       <c r="R172" t="n">
-        <v>7478131</v>
+        <v>7477946</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18305,10 +18305,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119677117</v>
+        <v>119677115</v>
       </c>
       <c r="B173" t="n">
-        <v>90846</v>
+        <v>57326</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18321,21 +18321,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18345,10 +18345,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>855412</v>
+        <v>855519</v>
       </c>
       <c r="R173" t="n">
-        <v>7478048</v>
+        <v>7478115</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18407,7 +18407,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119677127</v>
+        <v>119677123</v>
       </c>
       <c r="B174" t="n">
         <v>90580</v>
@@ -18447,10 +18447,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>855584</v>
+        <v>855409</v>
       </c>
       <c r="R174" t="n">
-        <v>7478103</v>
+        <v>7478024</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18509,10 +18509,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119677124</v>
+        <v>119677104</v>
       </c>
       <c r="B175" t="n">
-        <v>90580</v>
+        <v>104994</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18521,25 +18521,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>855474</v>
+        <v>855591</v>
       </c>
       <c r="R175" t="n">
-        <v>7478024</v>
+        <v>7478061</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18611,10 +18611,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119677146</v>
+        <v>119677132</v>
       </c>
       <c r="B176" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18627,21 +18627,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18651,10 +18651,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>855547</v>
+        <v>855595</v>
       </c>
       <c r="R176" t="n">
-        <v>7477962</v>
+        <v>7478061</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18713,10 +18713,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119677145</v>
+        <v>119677127</v>
       </c>
       <c r="B177" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18729,21 +18729,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18753,10 +18753,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>855589</v>
+        <v>855584</v>
       </c>
       <c r="R177" t="n">
-        <v>7477997</v>
+        <v>7478103</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18815,10 +18815,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119677138</v>
+        <v>119677117</v>
       </c>
       <c r="B178" t="n">
-        <v>82305</v>
+        <v>90846</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18831,21 +18831,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18855,10 +18855,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>855571</v>
+        <v>855412</v>
       </c>
       <c r="R178" t="n">
-        <v>7478136</v>
+        <v>7478048</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18917,7 +18917,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119677141</v>
+        <v>119677144</v>
       </c>
       <c r="B179" t="n">
         <v>82305</v>
@@ -18957,10 +18957,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>855579</v>
+        <v>855583</v>
       </c>
       <c r="R179" t="n">
-        <v>7478063</v>
+        <v>7478045</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19019,10 +19019,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119677121</v>
+        <v>119677124</v>
       </c>
       <c r="B180" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -19035,21 +19035,21 @@
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19059,10 +19059,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>855458</v>
+        <v>855474</v>
       </c>
       <c r="R180" t="n">
-        <v>7478069</v>
+        <v>7478024</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19223,10 +19223,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119677148</v>
+        <v>119677135</v>
       </c>
       <c r="B182" t="n">
-        <v>77458</v>
+        <v>82305</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19239,21 +19239,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19263,10 +19263,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>855572</v>
+        <v>855530</v>
       </c>
       <c r="R182" t="n">
-        <v>7477969</v>
+        <v>7478027</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -15656,10 +15656,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119677116</v>
+        <v>119677145</v>
       </c>
       <c r="B147" t="n">
-        <v>90334</v>
+        <v>82305</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15668,25 +15668,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>3215</v>
+        <v>1312</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15696,10 +15696,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>855497</v>
+        <v>855589</v>
       </c>
       <c r="R147" t="n">
-        <v>7477896</v>
+        <v>7477997</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15758,10 +15758,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119677145</v>
+        <v>119677116</v>
       </c>
       <c r="B148" t="n">
-        <v>82305</v>
+        <v>90334</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15770,25 +15770,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1312</v>
+        <v>3215</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15798,10 +15798,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>855589</v>
+        <v>855497</v>
       </c>
       <c r="R148" t="n">
-        <v>7477997</v>
+        <v>7477896</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -17795,10 +17795,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119677138</v>
+        <v>119677148</v>
       </c>
       <c r="B168" t="n">
-        <v>82305</v>
+        <v>77458</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17811,21 +17811,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1312</v>
+        <v>6487</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17835,10 +17835,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>855571</v>
+        <v>855572</v>
       </c>
       <c r="R168" t="n">
-        <v>7478136</v>
+        <v>7477969</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17897,10 +17897,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119677128</v>
+        <v>119677138</v>
       </c>
       <c r="B169" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17913,21 +17913,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17937,10 +17937,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>855591</v>
+        <v>855571</v>
       </c>
       <c r="R169" t="n">
-        <v>7478093</v>
+        <v>7478136</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17999,10 +17999,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119677110</v>
+        <v>119677128</v>
       </c>
       <c r="B170" t="n">
-        <v>90527</v>
+        <v>90580</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18011,25 +18011,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18039,10 +18039,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>855517</v>
+        <v>855591</v>
       </c>
       <c r="R170" t="n">
-        <v>7477955</v>
+        <v>7478093</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18101,10 +18101,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119677148</v>
+        <v>119677110</v>
       </c>
       <c r="B171" t="n">
-        <v>77458</v>
+        <v>90527</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18113,25 +18113,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6487</v>
+        <v>5447</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18141,10 +18141,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>855572</v>
+        <v>855517</v>
       </c>
       <c r="R171" t="n">
-        <v>7477969</v>
+        <v>7477955</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -18509,10 +18509,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119677104</v>
+        <v>119677127</v>
       </c>
       <c r="B175" t="n">
-        <v>104994</v>
+        <v>90580</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18521,25 +18521,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>855591</v>
+        <v>855584</v>
       </c>
       <c r="R175" t="n">
-        <v>7478061</v>
+        <v>7478103</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18611,10 +18611,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119677132</v>
+        <v>119677117</v>
       </c>
       <c r="B176" t="n">
-        <v>78526</v>
+        <v>90846</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18627,21 +18627,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18651,10 +18651,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>855595</v>
+        <v>855412</v>
       </c>
       <c r="R176" t="n">
-        <v>7478061</v>
+        <v>7478048</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18713,10 +18713,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119677127</v>
+        <v>119677132</v>
       </c>
       <c r="B177" t="n">
-        <v>90580</v>
+        <v>78526</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18729,21 +18729,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18753,10 +18753,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>855584</v>
+        <v>855595</v>
       </c>
       <c r="R177" t="n">
-        <v>7478103</v>
+        <v>7478061</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18815,10 +18815,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119677117</v>
+        <v>119677104</v>
       </c>
       <c r="B178" t="n">
-        <v>90846</v>
+        <v>104994</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18827,25 +18827,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>658</v>
+        <v>221725</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18855,10 +18855,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>855412</v>
+        <v>855591</v>
       </c>
       <c r="R178" t="n">
-        <v>7478048</v>
+        <v>7478061</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -17183,7 +17183,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119677136</v>
+        <v>119677142</v>
       </c>
       <c r="B162" t="n">
         <v>82305</v>
@@ -17223,10 +17223,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>855546</v>
+        <v>855580</v>
       </c>
       <c r="R162" t="n">
-        <v>7478132</v>
+        <v>7478058</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17285,10 +17285,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119677142</v>
+        <v>119677122</v>
       </c>
       <c r="B163" t="n">
-        <v>82305</v>
+        <v>90558</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17301,21 +17301,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17325,10 +17325,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>855580</v>
+        <v>855480</v>
       </c>
       <c r="R163" t="n">
-        <v>7478058</v>
+        <v>7478054</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17387,10 +17387,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119677122</v>
+        <v>119677141</v>
       </c>
       <c r="B164" t="n">
-        <v>90558</v>
+        <v>82305</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17403,21 +17403,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17427,10 +17427,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>855480</v>
+        <v>855579</v>
       </c>
       <c r="R164" t="n">
-        <v>7478054</v>
+        <v>7478063</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17489,7 +17489,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119677141</v>
+        <v>119677136</v>
       </c>
       <c r="B165" t="n">
         <v>82305</v>
@@ -17529,10 +17529,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>855579</v>
+        <v>855546</v>
       </c>
       <c r="R165" t="n">
-        <v>7478063</v>
+        <v>7478132</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17795,10 +17795,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119677148</v>
+        <v>119677138</v>
       </c>
       <c r="B168" t="n">
-        <v>77458</v>
+        <v>82305</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17811,21 +17811,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>6487</v>
+        <v>1312</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17835,10 +17835,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>855572</v>
+        <v>855571</v>
       </c>
       <c r="R168" t="n">
-        <v>7477969</v>
+        <v>7478136</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17897,10 +17897,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119677138</v>
+        <v>119677128</v>
       </c>
       <c r="B169" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17913,21 +17913,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17937,10 +17937,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>855571</v>
+        <v>855591</v>
       </c>
       <c r="R169" t="n">
-        <v>7478136</v>
+        <v>7478093</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17999,10 +17999,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119677128</v>
+        <v>119677110</v>
       </c>
       <c r="B170" t="n">
-        <v>90580</v>
+        <v>90527</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -18011,25 +18011,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18039,10 +18039,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>855591</v>
+        <v>855517</v>
       </c>
       <c r="R170" t="n">
-        <v>7478093</v>
+        <v>7477955</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18101,10 +18101,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119677110</v>
+        <v>119677148</v>
       </c>
       <c r="B171" t="n">
-        <v>90527</v>
+        <v>77458</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -18113,25 +18113,25 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>5447</v>
+        <v>6487</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -18141,10 +18141,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>855517</v>
+        <v>855572</v>
       </c>
       <c r="R171" t="n">
-        <v>7477955</v>
+        <v>7477969</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18509,10 +18509,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119677127</v>
+        <v>119677104</v>
       </c>
       <c r="B175" t="n">
-        <v>90580</v>
+        <v>104994</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18521,25 +18521,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18549,10 +18549,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>855584</v>
+        <v>855591</v>
       </c>
       <c r="R175" t="n">
-        <v>7478103</v>
+        <v>7478061</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18611,10 +18611,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119677117</v>
+        <v>119677132</v>
       </c>
       <c r="B176" t="n">
-        <v>90846</v>
+        <v>78526</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18627,21 +18627,21 @@
         </is>
       </c>
       <c r="E176" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18651,10 +18651,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>855412</v>
+        <v>855595</v>
       </c>
       <c r="R176" t="n">
-        <v>7478048</v>
+        <v>7478061</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18713,10 +18713,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119677132</v>
+        <v>119677127</v>
       </c>
       <c r="B177" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18729,21 +18729,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18753,10 +18753,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>855595</v>
+        <v>855584</v>
       </c>
       <c r="R177" t="n">
-        <v>7478061</v>
+        <v>7478103</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18815,10 +18815,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119677104</v>
+        <v>119677117</v>
       </c>
       <c r="B178" t="n">
-        <v>104994</v>
+        <v>90846</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18827,25 +18827,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>221725</v>
+        <v>658</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18855,10 +18855,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>855591</v>
+        <v>855412</v>
       </c>
       <c r="R178" t="n">
-        <v>7478061</v>
+        <v>7478048</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -9927,7 +9927,7 @@
         <v>117306813</v>
       </c>
       <c r="B91" t="n">
-        <v>86816</v>
+        <v>91357</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -9936,28 +9936,31 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>510</v>
+        <v>918</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Kuusivaaranoja, Nb</t>
@@ -10008,6 +10011,7 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY182"/>
+  <dimension ref="A1:AY192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19327,6 +19327,1032 @@
       </c>
       <c r="AY182" t="inlineStr"/>
     </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>121528343</v>
+      </c>
+      <c r="B183" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr"/>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>855872</v>
+      </c>
+      <c r="R183" t="n">
+        <v>7477436</v>
+      </c>
+      <c r="S183" t="n">
+        <v>10</v>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG183" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="inlineStr"/>
+      <c r="AW183" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX183" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>121528348</v>
+      </c>
+      <c r="B184" t="n">
+        <v>91109</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>855817</v>
+      </c>
+      <c r="R184" t="n">
+        <v>7477512</v>
+      </c>
+      <c r="S184" t="n">
+        <v>10</v>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="inlineStr"/>
+      <c r="AW184" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX184" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>121528342</v>
+      </c>
+      <c r="B185" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>855823</v>
+      </c>
+      <c r="R185" t="n">
+        <v>7477471</v>
+      </c>
+      <c r="S185" t="n">
+        <v>10</v>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG185" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="inlineStr"/>
+      <c r="AW185" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX185" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>121528338</v>
+      </c>
+      <c r="B186" t="n">
+        <v>90713</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>855886</v>
+      </c>
+      <c r="R186" t="n">
+        <v>7477459</v>
+      </c>
+      <c r="S186" t="n">
+        <v>10</v>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG186" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="inlineStr"/>
+      <c r="AW186" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX186" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>121528346</v>
+      </c>
+      <c r="B187" t="n">
+        <v>82391</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr"/>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>855883</v>
+      </c>
+      <c r="R187" t="n">
+        <v>7477479</v>
+      </c>
+      <c r="S187" t="n">
+        <v>10</v>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG187" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="inlineStr"/>
+      <c r="AW187" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX187" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>121528340</v>
+      </c>
+      <c r="B188" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>855894</v>
+      </c>
+      <c r="R188" t="n">
+        <v>7477350</v>
+      </c>
+      <c r="S188" t="n">
+        <v>10</v>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V188" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y188" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC188" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
+        </is>
+      </c>
+      <c r="AD188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT188" t="inlineStr"/>
+      <c r="AW188" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX188" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>121528345</v>
+      </c>
+      <c r="B189" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr"/>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q189" t="n">
+        <v>855858</v>
+      </c>
+      <c r="R189" t="n">
+        <v>7477466</v>
+      </c>
+      <c r="S189" t="n">
+        <v>10</v>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V189" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y189" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG189" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT189" t="inlineStr"/>
+      <c r="AW189" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX189" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>121528344</v>
+      </c>
+      <c r="B190" t="n">
+        <v>78607</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q190" t="n">
+        <v>855864</v>
+      </c>
+      <c r="R190" t="n">
+        <v>7477462</v>
+      </c>
+      <c r="S190" t="n">
+        <v>10</v>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V190" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y190" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG190" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT190" t="inlineStr"/>
+      <c r="AW190" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX190" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>121528341</v>
+      </c>
+      <c r="B191" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q191" t="n">
+        <v>855936</v>
+      </c>
+      <c r="R191" t="n">
+        <v>7477268</v>
+      </c>
+      <c r="S191" t="n">
+        <v>10</v>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V191" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y191" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG191" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT191" t="inlineStr"/>
+      <c r="AW191" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX191" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>121528339</v>
+      </c>
+      <c r="B192" t="n">
+        <v>57370</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>855816</v>
+      </c>
+      <c r="R192" t="n">
+        <v>7477504</v>
+      </c>
+      <c r="S192" t="n">
+        <v>10</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -19329,10 +19329,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121528343</v>
+        <v>121528339</v>
       </c>
       <c r="B183" t="n">
-        <v>78607</v>
+        <v>57371</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19345,21 +19345,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19369,10 +19369,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>855872</v>
+        <v>855816</v>
       </c>
       <c r="R183" t="n">
-        <v>7477436</v>
+        <v>7477504</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19431,10 +19431,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121528348</v>
+        <v>121528346</v>
       </c>
       <c r="B184" t="n">
-        <v>91109</v>
+        <v>82392</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19443,25 +19443,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4217</v>
+        <v>1312</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19471,10 +19471,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>855817</v>
+        <v>855883</v>
       </c>
       <c r="R184" t="n">
-        <v>7477512</v>
+        <v>7477479</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19515,7 +19515,6 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -19534,10 +19533,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121528342</v>
+        <v>121528344</v>
       </c>
       <c r="B185" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19574,10 +19573,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>855823</v>
+        <v>855864</v>
       </c>
       <c r="R185" t="n">
-        <v>7477471</v>
+        <v>7477462</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19636,10 +19635,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>121528338</v>
+        <v>121528348</v>
       </c>
       <c r="B186" t="n">
-        <v>90713</v>
+        <v>91115</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19648,25 +19647,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1202</v>
+        <v>4217</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19676,10 +19675,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>855886</v>
+        <v>855817</v>
       </c>
       <c r="R186" t="n">
-        <v>7477459</v>
+        <v>7477512</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19720,6 +19719,7 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
+      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
@@ -19738,10 +19738,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>121528346</v>
+        <v>121528341</v>
       </c>
       <c r="B187" t="n">
-        <v>82391</v>
+        <v>57371</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19754,21 +19754,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19778,10 +19778,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>855883</v>
+        <v>855936</v>
       </c>
       <c r="R187" t="n">
-        <v>7477479</v>
+        <v>7477268</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19843,7 +19843,7 @@
         <v>121528340</v>
       </c>
       <c r="B188" t="n">
-        <v>57370</v>
+        <v>57371</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19947,10 +19947,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>121528345</v>
+        <v>121528342</v>
       </c>
       <c r="B189" t="n">
-        <v>78607</v>
+        <v>78608</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19987,10 +19987,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>855858</v>
+        <v>855823</v>
       </c>
       <c r="R189" t="n">
-        <v>7477466</v>
+        <v>7477471</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20049,10 +20049,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121528344</v>
+        <v>121528338</v>
       </c>
       <c r="B190" t="n">
-        <v>78607</v>
+        <v>90719</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20065,21 +20065,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20089,10 +20089,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>855864</v>
+        <v>855886</v>
       </c>
       <c r="R190" t="n">
-        <v>7477462</v>
+        <v>7477459</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20151,10 +20151,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121528341</v>
+        <v>121528343</v>
       </c>
       <c r="B191" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20167,21 +20167,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20191,10 +20191,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>855936</v>
+        <v>855872</v>
       </c>
       <c r="R191" t="n">
-        <v>7477268</v>
+        <v>7477436</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20253,10 +20253,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121528339</v>
+        <v>121528345</v>
       </c>
       <c r="B192" t="n">
-        <v>57370</v>
+        <v>78608</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20269,21 +20269,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20293,10 +20293,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855816</v>
+        <v>855858</v>
       </c>
       <c r="R192" t="n">
-        <v>7477504</v>
+        <v>7477466</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -19329,10 +19329,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121528339</v>
+        <v>121528343</v>
       </c>
       <c r="B183" t="n">
-        <v>57371</v>
+        <v>78609</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19345,21 +19345,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19369,10 +19369,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>855816</v>
+        <v>855872</v>
       </c>
       <c r="R183" t="n">
-        <v>7477504</v>
+        <v>7477436</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19431,10 +19431,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121528346</v>
+        <v>121528348</v>
       </c>
       <c r="B184" t="n">
-        <v>82392</v>
+        <v>91116</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19443,25 +19443,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>1312</v>
+        <v>4217</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19471,10 +19471,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>855883</v>
+        <v>855817</v>
       </c>
       <c r="R184" t="n">
-        <v>7477479</v>
+        <v>7477512</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19515,6 +19515,7 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -19533,10 +19534,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121528344</v>
+        <v>121528338</v>
       </c>
       <c r="B185" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19549,21 +19550,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19573,10 +19574,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>855864</v>
+        <v>855886</v>
       </c>
       <c r="R185" t="n">
-        <v>7477462</v>
+        <v>7477459</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19635,10 +19636,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>121528348</v>
+        <v>121528346</v>
       </c>
       <c r="B186" t="n">
-        <v>91115</v>
+        <v>82393</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19647,25 +19648,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4217</v>
+        <v>1312</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19675,10 +19676,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>855817</v>
+        <v>855883</v>
       </c>
       <c r="R186" t="n">
-        <v>7477512</v>
+        <v>7477479</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19719,7 +19720,6 @@
       <c r="AE186" t="b">
         <v>0</v>
       </c>
-      <c r="AF186" t="inlineStr"/>
       <c r="AG186" t="b">
         <v>0</v>
       </c>
@@ -19738,10 +19738,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>121528341</v>
+        <v>121528344</v>
       </c>
       <c r="B187" t="n">
-        <v>57371</v>
+        <v>78609</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19754,21 +19754,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19778,10 +19778,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>855936</v>
+        <v>855864</v>
       </c>
       <c r="R187" t="n">
-        <v>7477268</v>
+        <v>7477462</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19840,10 +19840,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>121528340</v>
+        <v>121528342</v>
       </c>
       <c r="B188" t="n">
-        <v>57371</v>
+        <v>78609</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19856,21 +19856,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19880,10 +19880,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>855894</v>
+        <v>855823</v>
       </c>
       <c r="R188" t="n">
-        <v>7477350</v>
+        <v>7477471</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19916,11 +19916,6 @@
       <c r="AA188" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC188" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -19947,10 +19942,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>121528342</v>
+        <v>121528345</v>
       </c>
       <c r="B189" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19987,10 +19982,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>855823</v>
+        <v>855858</v>
       </c>
       <c r="R189" t="n">
-        <v>7477471</v>
+        <v>7477466</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20049,10 +20044,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121528338</v>
+        <v>121528341</v>
       </c>
       <c r="B190" t="n">
-        <v>90719</v>
+        <v>57372</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20065,21 +20060,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20089,10 +20084,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>855886</v>
+        <v>855936</v>
       </c>
       <c r="R190" t="n">
-        <v>7477459</v>
+        <v>7477268</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20151,10 +20146,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121528343</v>
+        <v>121528339</v>
       </c>
       <c r="B191" t="n">
-        <v>78608</v>
+        <v>57372</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20167,21 +20162,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20191,10 +20186,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>855872</v>
+        <v>855816</v>
       </c>
       <c r="R191" t="n">
-        <v>7477436</v>
+        <v>7477504</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20253,10 +20248,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121528345</v>
+        <v>121528340</v>
       </c>
       <c r="B192" t="n">
-        <v>78608</v>
+        <v>57372</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20269,21 +20264,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20293,10 +20288,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855858</v>
+        <v>855894</v>
       </c>
       <c r="R192" t="n">
-        <v>7477466</v>
+        <v>7477350</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20329,6 +20324,11 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -19329,10 +19329,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121528343</v>
+        <v>121528348</v>
       </c>
       <c r="B183" t="n">
-        <v>78609</v>
+        <v>91116</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19341,25 +19341,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19369,10 +19369,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>855872</v>
+        <v>855817</v>
       </c>
       <c r="R183" t="n">
-        <v>7477436</v>
+        <v>7477512</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19413,6 +19413,7 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
+      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19431,10 +19432,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121528348</v>
+        <v>121528344</v>
       </c>
       <c r="B184" t="n">
-        <v>91116</v>
+        <v>78609</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19443,25 +19444,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19471,10 +19472,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>855817</v>
+        <v>855864</v>
       </c>
       <c r="R184" t="n">
-        <v>7477512</v>
+        <v>7477462</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19515,7 +19516,6 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -19534,10 +19534,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121528338</v>
+        <v>121528342</v>
       </c>
       <c r="B185" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19550,21 +19550,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19574,10 +19574,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>855886</v>
+        <v>855823</v>
       </c>
       <c r="R185" t="n">
-        <v>7477459</v>
+        <v>7477471</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19636,10 +19636,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>121528346</v>
+        <v>121528343</v>
       </c>
       <c r="B186" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19652,21 +19652,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19676,10 +19676,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>855883</v>
+        <v>855872</v>
       </c>
       <c r="R186" t="n">
-        <v>7477479</v>
+        <v>7477436</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19738,10 +19738,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>121528344</v>
+        <v>121528340</v>
       </c>
       <c r="B187" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19754,21 +19754,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19778,10 +19778,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>855864</v>
+        <v>855894</v>
       </c>
       <c r="R187" t="n">
-        <v>7477462</v>
+        <v>7477350</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19814,6 +19814,11 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19840,7 +19845,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>121528342</v>
+        <v>121528345</v>
       </c>
       <c r="B188" t="n">
         <v>78609</v>
@@ -19880,10 +19885,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>855823</v>
+        <v>855858</v>
       </c>
       <c r="R188" t="n">
-        <v>7477471</v>
+        <v>7477466</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19942,10 +19947,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>121528345</v>
+        <v>121528341</v>
       </c>
       <c r="B189" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19958,21 +19963,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19982,10 +19987,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>855858</v>
+        <v>855936</v>
       </c>
       <c r="R189" t="n">
-        <v>7477466</v>
+        <v>7477268</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20044,10 +20049,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121528341</v>
+        <v>121528346</v>
       </c>
       <c r="B190" t="n">
-        <v>57372</v>
+        <v>82393</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20060,21 +20065,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20084,10 +20089,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>855936</v>
+        <v>855883</v>
       </c>
       <c r="R190" t="n">
-        <v>7477268</v>
+        <v>7477479</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20248,10 +20253,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121528340</v>
+        <v>121528338</v>
       </c>
       <c r="B192" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20264,21 +20269,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20288,10 +20293,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855894</v>
+        <v>855886</v>
       </c>
       <c r="R192" t="n">
-        <v>7477350</v>
+        <v>7477459</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20324,11 +20329,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -19329,10 +19329,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121528348</v>
+        <v>121528345</v>
       </c>
       <c r="B183" t="n">
-        <v>91116</v>
+        <v>78609</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19341,25 +19341,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19369,10 +19369,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>855817</v>
+        <v>855858</v>
       </c>
       <c r="R183" t="n">
-        <v>7477512</v>
+        <v>7477466</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19413,7 +19413,6 @@
       <c r="AE183" t="b">
         <v>0</v>
       </c>
-      <c r="AF183" t="inlineStr"/>
       <c r="AG183" t="b">
         <v>0</v>
       </c>
@@ -19432,10 +19431,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121528344</v>
+        <v>121528340</v>
       </c>
       <c r="B184" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19448,21 +19447,21 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19472,10 +19471,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>855864</v>
+        <v>855894</v>
       </c>
       <c r="R184" t="n">
-        <v>7477462</v>
+        <v>7477350</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19508,6 +19507,11 @@
       <c r="AA184" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -19534,10 +19538,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121528342</v>
+        <v>121528346</v>
       </c>
       <c r="B185" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19550,21 +19554,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19574,10 +19578,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>855823</v>
+        <v>855883</v>
       </c>
       <c r="R185" t="n">
-        <v>7477471</v>
+        <v>7477479</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19636,10 +19640,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>121528343</v>
+        <v>121528339</v>
       </c>
       <c r="B186" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19652,21 +19656,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19676,10 +19680,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>855872</v>
+        <v>855816</v>
       </c>
       <c r="R186" t="n">
-        <v>7477436</v>
+        <v>7477504</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19738,7 +19742,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>121528340</v>
+        <v>121528341</v>
       </c>
       <c r="B187" t="n">
         <v>57372</v>
@@ -19778,10 +19782,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>855894</v>
+        <v>855936</v>
       </c>
       <c r="R187" t="n">
-        <v>7477350</v>
+        <v>7477268</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19814,11 +19818,6 @@
       <c r="AA187" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC187" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -19845,7 +19844,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>121528345</v>
+        <v>121528343</v>
       </c>
       <c r="B188" t="n">
         <v>78609</v>
@@ -19885,10 +19884,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>855858</v>
+        <v>855872</v>
       </c>
       <c r="R188" t="n">
-        <v>7477466</v>
+        <v>7477436</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19947,10 +19946,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>121528341</v>
+        <v>121528344</v>
       </c>
       <c r="B189" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19963,21 +19962,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19987,10 +19986,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>855936</v>
+        <v>855864</v>
       </c>
       <c r="R189" t="n">
-        <v>7477268</v>
+        <v>7477462</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20049,10 +20048,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121528346</v>
+        <v>121528338</v>
       </c>
       <c r="B190" t="n">
-        <v>82393</v>
+        <v>90720</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20065,21 +20064,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>1312</v>
+        <v>1202</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20089,10 +20088,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>855883</v>
+        <v>855886</v>
       </c>
       <c r="R190" t="n">
-        <v>7477479</v>
+        <v>7477459</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20151,10 +20150,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121528339</v>
+        <v>121528348</v>
       </c>
       <c r="B191" t="n">
-        <v>57372</v>
+        <v>91116</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20163,25 +20162,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20191,10 +20190,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>855816</v>
+        <v>855817</v>
       </c>
       <c r="R191" t="n">
-        <v>7477504</v>
+        <v>7477512</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20235,6 +20234,7 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -20253,10 +20253,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121528338</v>
+        <v>121528342</v>
       </c>
       <c r="B192" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20269,21 +20269,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20293,10 +20293,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855886</v>
+        <v>855823</v>
       </c>
       <c r="R192" t="n">
-        <v>7477459</v>
+        <v>7477471</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -19329,10 +19329,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121528345</v>
+        <v>121528340</v>
       </c>
       <c r="B183" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19345,21 +19345,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19369,10 +19369,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>855858</v>
+        <v>855894</v>
       </c>
       <c r="R183" t="n">
-        <v>7477466</v>
+        <v>7477350</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19405,6 +19405,11 @@
       <c r="AA183" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -19431,10 +19436,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121528340</v>
+        <v>121528348</v>
       </c>
       <c r="B184" t="n">
-        <v>57372</v>
+        <v>91116</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19443,25 +19448,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19471,10 +19476,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>855894</v>
+        <v>855817</v>
       </c>
       <c r="R184" t="n">
-        <v>7477350</v>
+        <v>7477512</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19509,17 +19514,13 @@
           <t>2024-11-04</t>
         </is>
       </c>
-      <c r="AC184" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
-        </is>
-      </c>
       <c r="AD184" t="b">
         <v>0</v>
       </c>
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -19538,10 +19539,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121528346</v>
+        <v>121528343</v>
       </c>
       <c r="B185" t="n">
-        <v>82393</v>
+        <v>78609</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19554,21 +19555,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19578,10 +19579,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>855883</v>
+        <v>855872</v>
       </c>
       <c r="R185" t="n">
-        <v>7477479</v>
+        <v>7477436</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19640,10 +19641,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>121528339</v>
+        <v>121528344</v>
       </c>
       <c r="B186" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19656,21 +19657,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19680,10 +19681,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>855816</v>
+        <v>855864</v>
       </c>
       <c r="R186" t="n">
-        <v>7477504</v>
+        <v>7477462</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19844,10 +19845,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>121528343</v>
+        <v>121528346</v>
       </c>
       <c r="B188" t="n">
-        <v>78609</v>
+        <v>82393</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19860,21 +19861,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19884,10 +19885,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>855872</v>
+        <v>855883</v>
       </c>
       <c r="R188" t="n">
-        <v>7477436</v>
+        <v>7477479</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19946,7 +19947,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>121528344</v>
+        <v>121528342</v>
       </c>
       <c r="B189" t="n">
         <v>78609</v>
@@ -19986,10 +19987,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>855864</v>
+        <v>855823</v>
       </c>
       <c r="R189" t="n">
-        <v>7477462</v>
+        <v>7477471</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20150,10 +20151,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121528348</v>
+        <v>121528345</v>
       </c>
       <c r="B191" t="n">
-        <v>91116</v>
+        <v>78609</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20162,25 +20163,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20190,10 +20191,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>855817</v>
+        <v>855858</v>
       </c>
       <c r="R191" t="n">
-        <v>7477512</v>
+        <v>7477466</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20234,7 +20235,6 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -20253,10 +20253,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121528342</v>
+        <v>121528339</v>
       </c>
       <c r="B192" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20269,21 +20269,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20293,10 +20293,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855823</v>
+        <v>855816</v>
       </c>
       <c r="R192" t="n">
-        <v>7477471</v>
+        <v>7477504</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -19332,7 +19332,7 @@
         <v>121528340</v>
       </c>
       <c r="B183" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>121528348</v>
       </c>
       <c r="B184" t="n">
-        <v>91116</v>
+        <v>91124</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19539,10 +19539,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121528343</v>
+        <v>121528342</v>
       </c>
       <c r="B185" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19579,10 +19579,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>855872</v>
+        <v>855823</v>
       </c>
       <c r="R185" t="n">
-        <v>7477436</v>
+        <v>7477471</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19641,10 +19641,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>121528344</v>
+        <v>121528343</v>
       </c>
       <c r="B186" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19681,10 +19681,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>855864</v>
+        <v>855872</v>
       </c>
       <c r="R186" t="n">
-        <v>7477462</v>
+        <v>7477436</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19743,10 +19743,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>121528341</v>
+        <v>121528346</v>
       </c>
       <c r="B187" t="n">
-        <v>57372</v>
+        <v>82400</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19759,21 +19759,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19783,10 +19783,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>855936</v>
+        <v>855883</v>
       </c>
       <c r="R187" t="n">
-        <v>7477268</v>
+        <v>7477479</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19845,10 +19845,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>121528346</v>
+        <v>121528345</v>
       </c>
       <c r="B188" t="n">
-        <v>82393</v>
+        <v>78616</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19861,21 +19861,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19885,10 +19885,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>855883</v>
+        <v>855858</v>
       </c>
       <c r="R188" t="n">
-        <v>7477479</v>
+        <v>7477466</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19947,10 +19947,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>121528342</v>
+        <v>121528339</v>
       </c>
       <c r="B189" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19963,21 +19963,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19987,10 +19987,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>855823</v>
+        <v>855816</v>
       </c>
       <c r="R189" t="n">
-        <v>7477471</v>
+        <v>7477504</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20052,7 +20052,7 @@
         <v>121528338</v>
       </c>
       <c r="B190" t="n">
-        <v>90720</v>
+        <v>90728</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20151,10 +20151,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121528345</v>
+        <v>121528341</v>
       </c>
       <c r="B191" t="n">
-        <v>78609</v>
+        <v>57373</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20167,21 +20167,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20191,10 +20191,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>855858</v>
+        <v>855936</v>
       </c>
       <c r="R191" t="n">
-        <v>7477466</v>
+        <v>7477268</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20253,10 +20253,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121528339</v>
+        <v>121528344</v>
       </c>
       <c r="B192" t="n">
-        <v>57372</v>
+        <v>78616</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20269,21 +20269,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20293,10 +20293,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855816</v>
+        <v>855864</v>
       </c>
       <c r="R192" t="n">
-        <v>7477504</v>
+        <v>7477462</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -19329,10 +19329,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121528342</v>
+        <v>121528338</v>
       </c>
       <c r="B183" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19345,21 +19345,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19369,10 +19369,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>855823</v>
+        <v>855886</v>
       </c>
       <c r="R183" t="n">
-        <v>7477471</v>
+        <v>7477459</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19431,10 +19431,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121528339</v>
+        <v>121528348</v>
       </c>
       <c r="B184" t="n">
-        <v>57373</v>
+        <v>91124</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19443,25 +19443,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19471,10 +19471,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>855816</v>
+        <v>855817</v>
       </c>
       <c r="R184" t="n">
-        <v>7477504</v>
+        <v>7477512</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19515,6 +19515,7 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
+      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -19533,10 +19534,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121528348</v>
+        <v>121528341</v>
       </c>
       <c r="B185" t="n">
-        <v>91124</v>
+        <v>57373</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19545,25 +19546,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4217</v>
+        <v>100049</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19573,10 +19574,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>855817</v>
+        <v>855936</v>
       </c>
       <c r="R185" t="n">
-        <v>7477512</v>
+        <v>7477268</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19617,7 +19618,6 @@
       <c r="AE185" t="b">
         <v>0</v>
       </c>
-      <c r="AF185" t="inlineStr"/>
       <c r="AG185" t="b">
         <v>0</v>
       </c>
@@ -19636,10 +19636,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>121528346</v>
+        <v>121528343</v>
       </c>
       <c r="B186" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19652,21 +19652,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19676,10 +19676,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>855883</v>
+        <v>855872</v>
       </c>
       <c r="R186" t="n">
-        <v>7477479</v>
+        <v>7477436</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19738,10 +19738,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>121528344</v>
+        <v>121528346</v>
       </c>
       <c r="B187" t="n">
-        <v>78616</v>
+        <v>82400</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19754,21 +19754,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19778,10 +19778,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>855864</v>
+        <v>855883</v>
       </c>
       <c r="R187" t="n">
-        <v>7477462</v>
+        <v>7477479</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19840,10 +19840,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>121528338</v>
+        <v>121528345</v>
       </c>
       <c r="B188" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19856,21 +19856,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19880,10 +19880,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>855886</v>
+        <v>855858</v>
       </c>
       <c r="R188" t="n">
-        <v>7477459</v>
+        <v>7477466</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19942,7 +19942,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>121528343</v>
+        <v>121528342</v>
       </c>
       <c r="B189" t="n">
         <v>78616</v>
@@ -19982,10 +19982,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>855872</v>
+        <v>855823</v>
       </c>
       <c r="R189" t="n">
-        <v>7477436</v>
+        <v>7477471</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20044,7 +20044,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121528341</v>
+        <v>121528340</v>
       </c>
       <c r="B190" t="n">
         <v>57373</v>
@@ -20084,10 +20084,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>855936</v>
+        <v>855894</v>
       </c>
       <c r="R190" t="n">
-        <v>7477268</v>
+        <v>7477350</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20120,6 +20120,11 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20146,10 +20151,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121528345</v>
+        <v>121528339</v>
       </c>
       <c r="B191" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20162,21 +20167,21 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20186,10 +20191,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>855858</v>
+        <v>855816</v>
       </c>
       <c r="R191" t="n">
-        <v>7477466</v>
+        <v>7477504</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20248,10 +20253,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121528340</v>
+        <v>121528344</v>
       </c>
       <c r="B192" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20264,21 +20269,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20288,10 +20293,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855894</v>
+        <v>855864</v>
       </c>
       <c r="R192" t="n">
-        <v>7477350</v>
+        <v>7477462</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20324,11 +20329,6 @@
       <c r="AA192" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD192" t="b">

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -19329,10 +19329,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>121528338</v>
+        <v>121528344</v>
       </c>
       <c r="B183" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19345,21 +19345,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19369,10 +19369,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>855886</v>
+        <v>855864</v>
       </c>
       <c r="R183" t="n">
-        <v>7477459</v>
+        <v>7477462</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19431,10 +19431,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>121528348</v>
+        <v>121528346</v>
       </c>
       <c r="B184" t="n">
-        <v>91124</v>
+        <v>82400</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19443,25 +19443,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4217</v>
+        <v>1312</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19471,10 +19471,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>855817</v>
+        <v>855883</v>
       </c>
       <c r="R184" t="n">
-        <v>7477512</v>
+        <v>7477479</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19515,7 +19515,6 @@
       <c r="AE184" t="b">
         <v>0</v>
       </c>
-      <c r="AF184" t="inlineStr"/>
       <c r="AG184" t="b">
         <v>0</v>
       </c>
@@ -19534,7 +19533,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>121528341</v>
+        <v>121528340</v>
       </c>
       <c r="B185" t="n">
         <v>57373</v>
@@ -19574,10 +19573,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>855936</v>
+        <v>855894</v>
       </c>
       <c r="R185" t="n">
-        <v>7477268</v>
+        <v>7477350</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19610,6 +19609,11 @@
       <c r="AA185" t="inlineStr">
         <is>
           <t>2024-11-04</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -19636,10 +19640,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>121528343</v>
+        <v>121528341</v>
       </c>
       <c r="B186" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19652,21 +19656,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19676,10 +19680,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>855872</v>
+        <v>855936</v>
       </c>
       <c r="R186" t="n">
-        <v>7477436</v>
+        <v>7477268</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19738,10 +19742,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>121528346</v>
+        <v>121528345</v>
       </c>
       <c r="B187" t="n">
-        <v>82400</v>
+        <v>78616</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19754,21 +19758,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19778,10 +19782,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>855883</v>
+        <v>855858</v>
       </c>
       <c r="R187" t="n">
-        <v>7477479</v>
+        <v>7477466</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19840,7 +19844,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>121528345</v>
+        <v>121528343</v>
       </c>
       <c r="B188" t="n">
         <v>78616</v>
@@ -19880,10 +19884,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>855858</v>
+        <v>855872</v>
       </c>
       <c r="R188" t="n">
-        <v>7477466</v>
+        <v>7477436</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19942,10 +19946,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>121528342</v>
+        <v>121528338</v>
       </c>
       <c r="B189" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19958,21 +19962,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19982,10 +19986,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>855823</v>
+        <v>855886</v>
       </c>
       <c r="R189" t="n">
-        <v>7477471</v>
+        <v>7477459</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20044,10 +20048,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>121528340</v>
+        <v>121528342</v>
       </c>
       <c r="B190" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -20060,21 +20064,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -20084,10 +20088,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>855894</v>
+        <v>855823</v>
       </c>
       <c r="R190" t="n">
-        <v>7477350</v>
+        <v>7477471</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -20120,11 +20124,6 @@
       <c r="AA190" t="inlineStr">
         <is>
           <t>2024-11-04</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Hack hål</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -20151,10 +20150,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>121528339</v>
+        <v>121528348</v>
       </c>
       <c r="B191" t="n">
-        <v>57373</v>
+        <v>91124</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -20163,25 +20162,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100049</v>
+        <v>4217</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20191,10 +20190,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>855816</v>
+        <v>855817</v>
       </c>
       <c r="R191" t="n">
-        <v>7477504</v>
+        <v>7477512</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20235,6 +20234,7 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -20253,10 +20253,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>121528344</v>
+        <v>121528339</v>
       </c>
       <c r="B192" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20269,21 +20269,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20293,10 +20293,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855864</v>
+        <v>855816</v>
       </c>
       <c r="R192" t="n">
-        <v>7477462</v>
+        <v>7477504</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10441,11 +10441,11 @@
         <v>117306747</v>
       </c>
       <c r="B96" t="n">
-        <v>56499</v>
+        <v>56593</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -14016,11 +14016,11 @@
         <v>117306746</v>
       </c>
       <c r="B131" t="n">
-        <v>56499</v>
+        <v>56593</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -14322,11 +14322,11 @@
         <v>117306748</v>
       </c>
       <c r="B134" t="n">
-        <v>56499</v>
+        <v>56593</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -10441,11 +10441,11 @@
         <v>117306747</v>
       </c>
       <c r="B96" t="n">
-        <v>56593</v>
+        <v>56499</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -14016,11 +14016,11 @@
         <v>117306746</v>
       </c>
       <c r="B131" t="n">
-        <v>56593</v>
+        <v>56499</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -14322,11 +14322,11 @@
         <v>117306748</v>
       </c>
       <c r="B134" t="n">
-        <v>56593</v>
+        <v>56499</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY191"/>
+  <dimension ref="A1:AY194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20254,6 +20254,312 @@
       </c>
       <c r="AY191" t="inlineStr"/>
     </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>123699039</v>
+      </c>
+      <c r="B192" t="n">
+        <v>90931</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr"/>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>Torinen, Nb</t>
+        </is>
+      </c>
+      <c r="Q192" t="n">
+        <v>855161</v>
+      </c>
+      <c r="R192" t="n">
+        <v>7478256</v>
+      </c>
+      <c r="S192" t="n">
+        <v>15</v>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V192" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y192" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG192" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT192" t="inlineStr"/>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>123699078</v>
+      </c>
+      <c r="B193" t="n">
+        <v>82562</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr"/>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>Torinen, Nb</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>855203</v>
+      </c>
+      <c r="R193" t="n">
+        <v>7478335</v>
+      </c>
+      <c r="S193" t="n">
+        <v>15</v>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG193" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT193" t="inlineStr"/>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>123699076</v>
+      </c>
+      <c r="B194" t="n">
+        <v>82562</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr"/>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>Torinen, Nb</t>
+        </is>
+      </c>
+      <c r="Q194" t="n">
+        <v>855148</v>
+      </c>
+      <c r="R194" t="n">
+        <v>7478266</v>
+      </c>
+      <c r="S194" t="n">
+        <v>15</v>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V194" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W194" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y194" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AD194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG194" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT194" t="inlineStr"/>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20256,10 +20256,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>123699039</v>
+        <v>123699076</v>
       </c>
       <c r="B192" t="n">
-        <v>90931</v>
+        <v>82568</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20268,25 +20268,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20296,10 +20296,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855161</v>
+        <v>855148</v>
       </c>
       <c r="R192" t="n">
-        <v>7478256</v>
+        <v>7478266</v>
       </c>
       <c r="S192" t="n">
         <v>15</v>
@@ -20358,10 +20358,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>123699078</v>
+        <v>123699039</v>
       </c>
       <c r="B193" t="n">
-        <v>82562</v>
+        <v>90948</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20370,25 +20370,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20398,10 +20398,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>855203</v>
+        <v>855161</v>
       </c>
       <c r="R193" t="n">
-        <v>7478335</v>
+        <v>7478256</v>
       </c>
       <c r="S193" t="n">
         <v>15</v>
@@ -20460,10 +20460,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>123699076</v>
+        <v>123699078</v>
       </c>
       <c r="B194" t="n">
-        <v>82562</v>
+        <v>82568</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20500,10 +20500,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>855148</v>
+        <v>855203</v>
       </c>
       <c r="R194" t="n">
-        <v>7478266</v>
+        <v>7478335</v>
       </c>
       <c r="S194" t="n">
         <v>15</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20256,10 +20256,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>123699076</v>
+        <v>123699039</v>
       </c>
       <c r="B192" t="n">
-        <v>82568</v>
+        <v>90953</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20268,25 +20268,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20296,10 +20296,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855148</v>
+        <v>855161</v>
       </c>
       <c r="R192" t="n">
-        <v>7478266</v>
+        <v>7478256</v>
       </c>
       <c r="S192" t="n">
         <v>15</v>
@@ -20358,10 +20358,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>123699039</v>
+        <v>123699078</v>
       </c>
       <c r="B193" t="n">
-        <v>90948</v>
+        <v>82573</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20370,25 +20370,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20398,10 +20398,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>855161</v>
+        <v>855203</v>
       </c>
       <c r="R193" t="n">
-        <v>7478256</v>
+        <v>7478335</v>
       </c>
       <c r="S193" t="n">
         <v>15</v>
@@ -20460,10 +20460,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>123699078</v>
+        <v>123699076</v>
       </c>
       <c r="B194" t="n">
-        <v>82568</v>
+        <v>82573</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20500,10 +20500,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>855203</v>
+        <v>855148</v>
       </c>
       <c r="R194" t="n">
-        <v>7478335</v>
+        <v>7478266</v>
       </c>
       <c r="S194" t="n">
         <v>15</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20259,7 +20259,7 @@
         <v>123699039</v>
       </c>
       <c r="B192" t="n">
-        <v>90953</v>
+        <v>90955</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20358,10 +20358,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>123699078</v>
+        <v>123699076</v>
       </c>
       <c r="B193" t="n">
-        <v>82573</v>
+        <v>82575</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20398,10 +20398,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>855203</v>
+        <v>855148</v>
       </c>
       <c r="R193" t="n">
-        <v>7478335</v>
+        <v>7478266</v>
       </c>
       <c r="S193" t="n">
         <v>15</v>
@@ -20460,10 +20460,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>123699076</v>
+        <v>123699078</v>
       </c>
       <c r="B194" t="n">
-        <v>82573</v>
+        <v>82575</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20500,10 +20500,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>855148</v>
+        <v>855203</v>
       </c>
       <c r="R194" t="n">
-        <v>7478266</v>
+        <v>7478335</v>
       </c>
       <c r="S194" t="n">
         <v>15</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20256,10 +20256,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>123699039</v>
+        <v>123699078</v>
       </c>
       <c r="B192" t="n">
-        <v>90955</v>
+        <v>82575</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20268,25 +20268,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20296,10 +20296,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855161</v>
+        <v>855203</v>
       </c>
       <c r="R192" t="n">
-        <v>7478256</v>
+        <v>7478335</v>
       </c>
       <c r="S192" t="n">
         <v>15</v>
@@ -20460,10 +20460,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>123699078</v>
+        <v>123699039</v>
       </c>
       <c r="B194" t="n">
-        <v>82575</v>
+        <v>90955</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20472,25 +20472,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20500,10 +20500,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>855203</v>
+        <v>855161</v>
       </c>
       <c r="R194" t="n">
-        <v>7478335</v>
+        <v>7478256</v>
       </c>
       <c r="S194" t="n">
         <v>15</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20256,7 +20256,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>123699078</v>
+        <v>123699076</v>
       </c>
       <c r="B192" t="n">
         <v>82575</v>
@@ -20296,10 +20296,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855203</v>
+        <v>855148</v>
       </c>
       <c r="R192" t="n">
-        <v>7478335</v>
+        <v>7478266</v>
       </c>
       <c r="S192" t="n">
         <v>15</v>
@@ -20358,7 +20358,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>123699076</v>
+        <v>123699078</v>
       </c>
       <c r="B193" t="n">
         <v>82575</v>
@@ -20398,10 +20398,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>855148</v>
+        <v>855203</v>
       </c>
       <c r="R193" t="n">
-        <v>7478266</v>
+        <v>7478335</v>
       </c>
       <c r="S193" t="n">
         <v>15</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20256,7 +20256,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>123699076</v>
+        <v>123699078</v>
       </c>
       <c r="B192" t="n">
         <v>82575</v>
@@ -20296,10 +20296,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>855148</v>
+        <v>855203</v>
       </c>
       <c r="R192" t="n">
-        <v>7478266</v>
+        <v>7478335</v>
       </c>
       <c r="S192" t="n">
         <v>15</v>
@@ -20358,10 +20358,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>123699078</v>
+        <v>123699039</v>
       </c>
       <c r="B193" t="n">
-        <v>82575</v>
+        <v>90955</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20370,25 +20370,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20398,10 +20398,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>855203</v>
+        <v>855161</v>
       </c>
       <c r="R193" t="n">
-        <v>7478335</v>
+        <v>7478256</v>
       </c>
       <c r="S193" t="n">
         <v>15</v>
@@ -20460,10 +20460,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>123699039</v>
+        <v>123699076</v>
       </c>
       <c r="B194" t="n">
-        <v>90955</v>
+        <v>82575</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20472,25 +20472,25 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20500,10 +20500,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>855161</v>
+        <v>855148</v>
       </c>
       <c r="R194" t="n">
-        <v>7478256</v>
+        <v>7478266</v>
       </c>
       <c r="S194" t="n">
         <v>15</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY194"/>
+  <dimension ref="A1:AY199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20560,6 +20560,533 @@
       </c>
       <c r="AY194" t="inlineStr"/>
     </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>124855492</v>
+      </c>
+      <c r="B195" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q195" t="n">
+        <v>855343</v>
+      </c>
+      <c r="R195" t="n">
+        <v>7478123</v>
+      </c>
+      <c r="S195" t="n">
+        <v>10</v>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG195" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT195" t="inlineStr"/>
+      <c r="AW195" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX195" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>124855483</v>
+      </c>
+      <c r="B196" t="n">
+        <v>78810</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q196" t="n">
+        <v>855251</v>
+      </c>
+      <c r="R196" t="n">
+        <v>7478036</v>
+      </c>
+      <c r="S196" t="n">
+        <v>10</v>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V196" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y196" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG196" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT196" t="inlineStr"/>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>124855481</v>
+      </c>
+      <c r="B197" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q197" t="n">
+        <v>855337</v>
+      </c>
+      <c r="R197" t="n">
+        <v>7478074</v>
+      </c>
+      <c r="S197" t="n">
+        <v>10</v>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG197" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT197" t="inlineStr"/>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>124855535</v>
+      </c>
+      <c r="B198" t="n">
+        <v>83424</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr"/>
+      <c r="K198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q198" t="n">
+        <v>855041</v>
+      </c>
+      <c r="R198" t="n">
+        <v>7477819</v>
+      </c>
+      <c r="S198" t="n">
+        <v>10</v>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V198" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W198" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y198" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
+      <c r="AD198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF198" t="inlineStr"/>
+      <c r="AG198" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT198" t="inlineStr"/>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>124855493</v>
+      </c>
+      <c r="B199" t="n">
+        <v>82597</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q199" t="n">
+        <v>855343</v>
+      </c>
+      <c r="R199" t="n">
+        <v>7478075</v>
+      </c>
+      <c r="S199" t="n">
+        <v>10</v>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG199" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT199" t="inlineStr"/>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855492</v>
+        <v>124855483</v>
       </c>
       <c r="B195" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20578,21 +20578,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855343</v>
+        <v>855251</v>
       </c>
       <c r="R195" t="n">
-        <v>7478123</v>
+        <v>7478036</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20664,10 +20664,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855483</v>
+        <v>124855481</v>
       </c>
       <c r="B196" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20680,21 +20680,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20704,10 +20704,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855251</v>
+        <v>855337</v>
       </c>
       <c r="R196" t="n">
-        <v>7478036</v>
+        <v>7478074</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20766,10 +20766,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855481</v>
+        <v>124855493</v>
       </c>
       <c r="B197" t="n">
-        <v>91008</v>
+        <v>82597</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20782,21 +20782,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20806,10 +20806,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855337</v>
+        <v>855343</v>
       </c>
       <c r="R197" t="n">
-        <v>7478074</v>
+        <v>7478075</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20987,7 +20987,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855493</v>
+        <v>124855492</v>
       </c>
       <c r="B199" t="n">
         <v>82597</v>
@@ -21030,7 +21030,7 @@
         <v>855343</v>
       </c>
       <c r="R199" t="n">
-        <v>7478075</v>
+        <v>7478123</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855483</v>
+        <v>124855481</v>
       </c>
       <c r="B195" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20578,21 +20578,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855251</v>
+        <v>855337</v>
       </c>
       <c r="R195" t="n">
-        <v>7478036</v>
+        <v>7478074</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20664,10 +20664,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855481</v>
+        <v>124855535</v>
       </c>
       <c r="B196" t="n">
-        <v>91008</v>
+        <v>83424</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20676,38 +20676,45 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1108</v>
+        <v>1445</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855337</v>
+        <v>855041</v>
       </c>
       <c r="R196" t="n">
-        <v>7478074</v>
+        <v>7477819</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20742,12 +20749,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20762,7 +20775,11 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY196" t="inlineStr"/>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20868,10 +20885,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124855535</v>
+        <v>124855492</v>
       </c>
       <c r="B198" t="n">
-        <v>83424</v>
+        <v>82597</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20880,45 +20897,38 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I198" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J198" t="inlineStr"/>
-      <c r="K198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R198" t="n">
-        <v>7477819</v>
+        <v>7478123</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20953,18 +20963,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC198" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD198" t="b">
         <v>0</v>
       </c>
       <c r="AE198" t="b">
         <v>0</v>
       </c>
-      <c r="AF198" t="inlineStr"/>
       <c r="AG198" t="b">
         <v>0</v>
       </c>
@@ -20979,18 +20983,14 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY198" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855492</v>
+        <v>124855483</v>
       </c>
       <c r="B199" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21003,21 +21003,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21027,10 +21027,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>855343</v>
+        <v>855251</v>
       </c>
       <c r="R199" t="n">
-        <v>7478123</v>
+        <v>7478036</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855481</v>
+        <v>124855535</v>
       </c>
       <c r="B195" t="n">
-        <v>91008</v>
+        <v>83424</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20574,38 +20574,45 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1108</v>
+        <v>1445</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855337</v>
+        <v>855041</v>
       </c>
       <c r="R195" t="n">
-        <v>7478074</v>
+        <v>7477819</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20640,12 +20647,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20660,14 +20673,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY195" t="inlineStr"/>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855535</v>
+        <v>124855483</v>
       </c>
       <c r="B196" t="n">
-        <v>83424</v>
+        <v>78810</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20676,45 +20693,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1445</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855041</v>
+        <v>855251</v>
       </c>
       <c r="R196" t="n">
-        <v>7477819</v>
+        <v>7478036</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20749,18 +20759,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20775,15 +20779,11 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY196" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855493</v>
+        <v>124855492</v>
       </c>
       <c r="B197" t="n">
         <v>82597</v>
@@ -20826,7 +20826,7 @@
         <v>855343</v>
       </c>
       <c r="R197" t="n">
-        <v>7478075</v>
+        <v>7478123</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20885,7 +20885,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124855492</v>
+        <v>124855493</v>
       </c>
       <c r="B198" t="n">
         <v>82597</v>
@@ -20928,7 +20928,7 @@
         <v>855343</v>
       </c>
       <c r="R198" t="n">
-        <v>7478123</v>
+        <v>7478075</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20987,10 +20987,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855483</v>
+        <v>124855481</v>
       </c>
       <c r="B199" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21003,21 +21003,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21027,10 +21027,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>855251</v>
+        <v>855337</v>
       </c>
       <c r="R199" t="n">
-        <v>7478036</v>
+        <v>7478074</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855535</v>
+        <v>124855493</v>
       </c>
       <c r="B195" t="n">
-        <v>83424</v>
+        <v>82597</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20574,45 +20574,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R195" t="n">
-        <v>7477819</v>
+        <v>7478075</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20647,18 +20640,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20673,18 +20660,14 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY195" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855483</v>
+        <v>124855535</v>
       </c>
       <c r="B196" t="n">
-        <v>78810</v>
+        <v>83424</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20693,38 +20676,45 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>1445</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855251</v>
+        <v>855041</v>
       </c>
       <c r="R196" t="n">
-        <v>7478036</v>
+        <v>7477819</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20759,12 +20749,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20779,7 +20775,11 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY196" t="inlineStr"/>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -20885,10 +20885,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124855493</v>
+        <v>124855483</v>
       </c>
       <c r="B198" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20901,21 +20901,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>855343</v>
+        <v>855251</v>
       </c>
       <c r="R198" t="n">
-        <v>7478075</v>
+        <v>7478036</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855493</v>
+        <v>124855535</v>
       </c>
       <c r="B195" t="n">
-        <v>82597</v>
+        <v>83424</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20574,38 +20574,45 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1312</v>
+        <v>1445</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855343</v>
+        <v>855041</v>
       </c>
       <c r="R195" t="n">
-        <v>7478075</v>
+        <v>7477819</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20640,12 +20647,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20660,14 +20673,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY195" t="inlineStr"/>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855535</v>
+        <v>124855492</v>
       </c>
       <c r="B196" t="n">
-        <v>83424</v>
+        <v>82597</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20676,45 +20693,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R196" t="n">
-        <v>7477819</v>
+        <v>7478123</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20749,18 +20759,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20775,18 +20779,14 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY196" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855492</v>
+        <v>124855481</v>
       </c>
       <c r="B197" t="n">
-        <v>82597</v>
+        <v>91008</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20799,21 +20799,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20823,10 +20823,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855343</v>
+        <v>855337</v>
       </c>
       <c r="R197" t="n">
-        <v>7478123</v>
+        <v>7478074</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20885,10 +20885,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124855483</v>
+        <v>124855493</v>
       </c>
       <c r="B198" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20901,21 +20901,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>855251</v>
+        <v>855343</v>
       </c>
       <c r="R198" t="n">
-        <v>7478036</v>
+        <v>7478075</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20987,10 +20987,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855481</v>
+        <v>124855483</v>
       </c>
       <c r="B199" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21003,21 +21003,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21027,10 +21027,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>855337</v>
+        <v>855251</v>
       </c>
       <c r="R199" t="n">
-        <v>7478074</v>
+        <v>7478036</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855535</v>
+        <v>124855493</v>
       </c>
       <c r="B195" t="n">
-        <v>83424</v>
+        <v>82597</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20574,45 +20574,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R195" t="n">
-        <v>7477819</v>
+        <v>7478075</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20647,18 +20640,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20673,18 +20660,14 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY195" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855492</v>
+        <v>124855481</v>
       </c>
       <c r="B196" t="n">
-        <v>82597</v>
+        <v>91008</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20697,21 +20680,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20721,10 +20704,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855343</v>
+        <v>855337</v>
       </c>
       <c r="R196" t="n">
-        <v>7478123</v>
+        <v>7478074</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20783,10 +20766,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855481</v>
+        <v>124855535</v>
       </c>
       <c r="B197" t="n">
-        <v>91008</v>
+        <v>83424</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20795,38 +20778,45 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1108</v>
+        <v>1445</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855337</v>
+        <v>855041</v>
       </c>
       <c r="R197" t="n">
-        <v>7478074</v>
+        <v>7477819</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20861,12 +20851,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -20881,14 +20877,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr"/>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124855493</v>
+        <v>124855483</v>
       </c>
       <c r="B198" t="n">
-        <v>82597</v>
+        <v>78810</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20901,21 +20901,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>855343</v>
+        <v>855251</v>
       </c>
       <c r="R198" t="n">
-        <v>7478075</v>
+        <v>7478036</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20987,10 +20987,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855483</v>
+        <v>124855492</v>
       </c>
       <c r="B199" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21003,21 +21003,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21027,10 +21027,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>855251</v>
+        <v>855343</v>
       </c>
       <c r="R199" t="n">
-        <v>7478036</v>
+        <v>7478123</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855493</v>
+        <v>124855481</v>
       </c>
       <c r="B195" t="n">
-        <v>82597</v>
+        <v>91008</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20578,21 +20578,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855343</v>
+        <v>855337</v>
       </c>
       <c r="R195" t="n">
-        <v>7478075</v>
+        <v>7478074</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20664,10 +20664,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855481</v>
+        <v>124855535</v>
       </c>
       <c r="B196" t="n">
-        <v>91008</v>
+        <v>83424</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20676,38 +20676,45 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1108</v>
+        <v>1445</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855337</v>
+        <v>855041</v>
       </c>
       <c r="R196" t="n">
-        <v>7478074</v>
+        <v>7477819</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20742,12 +20749,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20762,14 +20775,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY196" t="inlineStr"/>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855535</v>
+        <v>124855492</v>
       </c>
       <c r="B197" t="n">
-        <v>83424</v>
+        <v>82597</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20778,45 +20795,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R197" t="n">
-        <v>7477819</v>
+        <v>7478123</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20851,18 +20861,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -20877,11 +20881,7 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -20987,7 +20987,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855492</v>
+        <v>124855493</v>
       </c>
       <c r="B199" t="n">
         <v>82597</v>
@@ -21030,7 +21030,7 @@
         <v>855343</v>
       </c>
       <c r="R199" t="n">
-        <v>7478123</v>
+        <v>7478075</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855481</v>
+        <v>124855535</v>
       </c>
       <c r="B195" t="n">
-        <v>91008</v>
+        <v>83424</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20574,38 +20574,45 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1108</v>
+        <v>1445</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855337</v>
+        <v>855041</v>
       </c>
       <c r="R195" t="n">
-        <v>7478074</v>
+        <v>7477819</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20640,12 +20647,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20660,14 +20673,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY195" t="inlineStr"/>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855535</v>
+        <v>124855493</v>
       </c>
       <c r="B196" t="n">
-        <v>83424</v>
+        <v>82597</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20676,45 +20693,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R196" t="n">
-        <v>7477819</v>
+        <v>7478075</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20749,18 +20759,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20775,18 +20779,14 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY196" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855492</v>
+        <v>124855481</v>
       </c>
       <c r="B197" t="n">
-        <v>82597</v>
+        <v>91008</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20799,21 +20799,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20823,10 +20823,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855343</v>
+        <v>855337</v>
       </c>
       <c r="R197" t="n">
-        <v>7478123</v>
+        <v>7478074</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20987,7 +20987,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855493</v>
+        <v>124855492</v>
       </c>
       <c r="B199" t="n">
         <v>82597</v>
@@ -21030,7 +21030,7 @@
         <v>855343</v>
       </c>
       <c r="R199" t="n">
-        <v>7478075</v>
+        <v>7478123</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855535</v>
+        <v>124855483</v>
       </c>
       <c r="B195" t="n">
-        <v>83424</v>
+        <v>78810</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20574,45 +20574,38 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1445</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855041</v>
+        <v>855251</v>
       </c>
       <c r="R195" t="n">
-        <v>7477819</v>
+        <v>7478036</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20647,18 +20640,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
-      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20673,18 +20660,14 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY195" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855493</v>
+        <v>124855535</v>
       </c>
       <c r="B196" t="n">
-        <v>82597</v>
+        <v>83424</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20693,38 +20676,45 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1312</v>
+        <v>1445</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr"/>
+      <c r="K196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855343</v>
+        <v>855041</v>
       </c>
       <c r="R196" t="n">
-        <v>7478075</v>
+        <v>7477819</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20759,12 +20749,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
+      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20779,14 +20775,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY196" t="inlineStr"/>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855481</v>
+        <v>124855492</v>
       </c>
       <c r="B197" t="n">
-        <v>91008</v>
+        <v>82597</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20799,21 +20799,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1108</v>
+        <v>1312</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20823,10 +20823,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855337</v>
+        <v>855343</v>
       </c>
       <c r="R197" t="n">
-        <v>7478074</v>
+        <v>7478123</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20885,10 +20885,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124855483</v>
+        <v>124855481</v>
       </c>
       <c r="B198" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20901,21 +20901,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>855251</v>
+        <v>855337</v>
       </c>
       <c r="R198" t="n">
-        <v>7478036</v>
+        <v>7478074</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20987,7 +20987,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855492</v>
+        <v>124855493</v>
       </c>
       <c r="B199" t="n">
         <v>82597</v>
@@ -21030,7 +21030,7 @@
         <v>855343</v>
       </c>
       <c r="R199" t="n">
-        <v>7478123</v>
+        <v>7478075</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855483</v>
+        <v>124855481</v>
       </c>
       <c r="B195" t="n">
-        <v>78810</v>
+        <v>91008</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20578,21 +20578,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855251</v>
+        <v>855337</v>
       </c>
       <c r="R195" t="n">
-        <v>7478036</v>
+        <v>7478074</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20664,10 +20664,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855535</v>
+        <v>124855492</v>
       </c>
       <c r="B196" t="n">
-        <v>83424</v>
+        <v>82597</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20676,45 +20676,38 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I196" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R196" t="n">
-        <v>7477819</v>
+        <v>7478123</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20749,18 +20742,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD196" t="b">
         <v>0</v>
       </c>
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -20775,18 +20762,14 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY196" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855492</v>
+        <v>124855535</v>
       </c>
       <c r="B197" t="n">
-        <v>82597</v>
+        <v>83424</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20795,38 +20778,45 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1312</v>
+        <v>1445</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855343</v>
+        <v>855041</v>
       </c>
       <c r="R197" t="n">
-        <v>7478123</v>
+        <v>7477819</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20861,12 +20851,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -20881,14 +20877,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr"/>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124855481</v>
+        <v>124855483</v>
       </c>
       <c r="B198" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20901,21 +20901,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>855337</v>
+        <v>855251</v>
       </c>
       <c r="R198" t="n">
-        <v>7478074</v>
+        <v>7478036</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855481</v>
+        <v>124855483</v>
       </c>
       <c r="B195" t="n">
-        <v>91008</v>
+        <v>78810</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20578,21 +20578,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855337</v>
+        <v>855251</v>
       </c>
       <c r="R195" t="n">
-        <v>7478074</v>
+        <v>7478036</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20664,10 +20664,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855492</v>
+        <v>124855481</v>
       </c>
       <c r="B196" t="n">
-        <v>82597</v>
+        <v>91008</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20680,21 +20680,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20704,10 +20704,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855343</v>
+        <v>855337</v>
       </c>
       <c r="R196" t="n">
-        <v>7478123</v>
+        <v>7478074</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20766,10 +20766,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855535</v>
+        <v>124855492</v>
       </c>
       <c r="B197" t="n">
-        <v>83424</v>
+        <v>82597</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20778,45 +20778,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R197" t="n">
-        <v>7477819</v>
+        <v>7478123</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20851,18 +20844,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -20877,18 +20864,14 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124855483</v>
+        <v>124855493</v>
       </c>
       <c r="B198" t="n">
-        <v>78810</v>
+        <v>82597</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20901,21 +20884,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20925,10 +20908,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>855251</v>
+        <v>855343</v>
       </c>
       <c r="R198" t="n">
-        <v>7478036</v>
+        <v>7478075</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20987,10 +20970,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855493</v>
+        <v>124855535</v>
       </c>
       <c r="B199" t="n">
-        <v>82597</v>
+        <v>83424</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20999,38 +20982,45 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1312</v>
+        <v>1445</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr"/>
+      <c r="K199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>855343</v>
+        <v>855041</v>
       </c>
       <c r="R199" t="n">
-        <v>7478075</v>
+        <v>7477819</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21065,12 +21055,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
+      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -21085,7 +21081,11 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY199" t="inlineStr"/>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855483</v>
+        <v>124855481</v>
       </c>
       <c r="B195" t="n">
-        <v>78810</v>
+        <v>91162</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20578,21 +20578,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20602,10 +20602,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855251</v>
+        <v>855337</v>
       </c>
       <c r="R195" t="n">
-        <v>7478036</v>
+        <v>7478074</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20664,10 +20664,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855481</v>
+        <v>124855483</v>
       </c>
       <c r="B196" t="n">
-        <v>91008</v>
+        <v>78947</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20680,21 +20680,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20704,10 +20704,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855337</v>
+        <v>855251</v>
       </c>
       <c r="R196" t="n">
-        <v>7478074</v>
+        <v>7478036</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20766,10 +20766,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855492</v>
+        <v>124855535</v>
       </c>
       <c r="B197" t="n">
-        <v>82597</v>
+        <v>83564</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20778,38 +20778,45 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1312</v>
+        <v>1445</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr"/>
+      <c r="K197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855343</v>
+        <v>855041</v>
       </c>
       <c r="R197" t="n">
-        <v>7478123</v>
+        <v>7477819</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20844,12 +20851,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
+      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -20864,14 +20877,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr"/>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
         <v>124855493</v>
       </c>
       <c r="B198" t="n">
-        <v>82597</v>
+        <v>82737</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20970,10 +20987,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855535</v>
+        <v>124855492</v>
       </c>
       <c r="B199" t="n">
-        <v>83424</v>
+        <v>82737</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20982,45 +20999,38 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr"/>
-      <c r="K199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R199" t="n">
-        <v>7477819</v>
+        <v>7478123</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -21055,18 +21065,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC199" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD199" t="b">
         <v>0</v>
       </c>
       <c r="AE199" t="b">
         <v>0</v>
       </c>
-      <c r="AF199" t="inlineStr"/>
       <c r="AG199" t="b">
         <v>0</v>
       </c>
@@ -21081,11 +21085,7 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY199" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY199" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -20562,10 +20562,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>124855481</v>
+        <v>124855535</v>
       </c>
       <c r="B195" t="n">
-        <v>91162</v>
+        <v>83564</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20574,38 +20574,45 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1108</v>
+        <v>1445</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I195" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr"/>
+      <c r="K195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
       <c r="P195" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>855337</v>
+        <v>855041</v>
       </c>
       <c r="R195" t="n">
-        <v>7478074</v>
+        <v>7477819</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20640,12 +20647,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
       <c r="AD195" t="b">
         <v>0</v>
       </c>
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20660,14 +20673,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY195" t="inlineStr"/>
+      <c r="AY195" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla 2025</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>124855483</v>
+        <v>124855492</v>
       </c>
       <c r="B196" t="n">
-        <v>78947</v>
+        <v>82737</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
@@ -20680,21 +20697,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -20704,10 +20721,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>855251</v>
+        <v>855343</v>
       </c>
       <c r="R196" t="n">
-        <v>7478036</v>
+        <v>7478123</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20766,10 +20783,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>124855535</v>
+        <v>124855493</v>
       </c>
       <c r="B197" t="n">
-        <v>83564</v>
+        <v>82737</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20778,45 +20795,38 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I197" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J197" t="inlineStr"/>
-      <c r="K197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>855041</v>
+        <v>855343</v>
       </c>
       <c r="R197" t="n">
-        <v>7477819</v>
+        <v>7478075</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20851,18 +20861,12 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="AC197" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
-        </is>
-      </c>
       <c r="AD197" t="b">
         <v>0</v>
       </c>
       <c r="AE197" t="b">
         <v>0</v>
       </c>
-      <c r="AF197" t="inlineStr"/>
       <c r="AG197" t="b">
         <v>0</v>
       </c>
@@ -20877,18 +20881,14 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY197" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>124855493</v>
+        <v>124855483</v>
       </c>
       <c r="B198" t="n">
-        <v>82737</v>
+        <v>78947</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20901,21 +20901,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20925,10 +20925,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>855343</v>
+        <v>855251</v>
       </c>
       <c r="R198" t="n">
-        <v>7478075</v>
+        <v>7478036</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20987,10 +20987,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>124855492</v>
+        <v>124855481</v>
       </c>
       <c r="B199" t="n">
-        <v>82737</v>
+        <v>91162</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -21003,21 +21003,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1312</v>
+        <v>1108</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -21027,10 +21027,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>855343</v>
+        <v>855337</v>
       </c>
       <c r="R199" t="n">
-        <v>7478123</v>
+        <v>7478074</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6632,10 +6632,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119677122</v>
+        <v>119677118</v>
       </c>
       <c r="B60" t="n">
-        <v>90558</v>
+        <v>96856</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6644,27 +6644,23 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1108</v>
+        <v>221944</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -6672,10 +6668,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855480</v>
+        <v>855491</v>
       </c>
       <c r="R60" t="n">
-        <v>7478054</v>
+        <v>7477890</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6716,6 +6712,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6734,10 +6731,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119677113</v>
+        <v>119677122</v>
       </c>
       <c r="B61" t="n">
-        <v>90562</v>
+        <v>90558</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6750,21 +6747,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6774,10 +6771,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855429</v>
+        <v>855480</v>
       </c>
       <c r="R61" t="n">
-        <v>7478011</v>
+        <v>7478054</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6836,10 +6833,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119677110</v>
+        <v>119677113</v>
       </c>
       <c r="B62" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6848,25 +6845,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6876,10 +6873,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855517</v>
+        <v>855429</v>
       </c>
       <c r="R62" t="n">
-        <v>7477955</v>
+        <v>7478011</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6938,10 +6935,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119677133</v>
+        <v>119677110</v>
       </c>
       <c r="B63" t="n">
-        <v>82305</v>
+        <v>90527</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6950,25 +6947,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6978,10 +6975,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855497</v>
+        <v>855517</v>
       </c>
       <c r="R63" t="n">
-        <v>7477946</v>
+        <v>7477955</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7040,10 +7037,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119677123</v>
+        <v>119677133</v>
       </c>
       <c r="B64" t="n">
-        <v>90580</v>
+        <v>82305</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7056,21 +7053,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7080,10 +7077,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855409</v>
+        <v>855497</v>
       </c>
       <c r="R64" t="n">
-        <v>7478024</v>
+        <v>7477946</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7142,10 +7139,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119677117</v>
+        <v>119677123</v>
       </c>
       <c r="B65" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7158,21 +7155,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7182,10 +7179,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>855412</v>
+        <v>855409</v>
       </c>
       <c r="R65" t="n">
-        <v>7478048</v>
+        <v>7478024</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7244,10 +7241,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119677124</v>
+        <v>119677117</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>90846</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7260,21 +7257,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7284,10 +7281,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855474</v>
+        <v>855412</v>
       </c>
       <c r="R66" t="n">
-        <v>7478024</v>
+        <v>7478048</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7346,10 +7343,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119677135</v>
+        <v>119677124</v>
       </c>
       <c r="B67" t="n">
-        <v>82305</v>
+        <v>90580</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7362,21 +7359,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1312</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7386,10 +7383,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>855530</v>
+        <v>855474</v>
       </c>
       <c r="R67" t="n">
-        <v>7478027</v>
+        <v>7478024</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7448,10 +7445,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123699075</v>
+        <v>119677135</v>
       </c>
       <c r="B68" t="n">
-        <v>82597</v>
+        <v>82305</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7488,13 +7485,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>855207</v>
+        <v>855530</v>
       </c>
       <c r="R68" t="n">
-        <v>7477876</v>
+        <v>7478027</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7518,12 +7515,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7550,55 +7547,53 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124855535</v>
+        <v>123699075</v>
       </c>
       <c r="B69" t="n">
-        <v>83564</v>
+        <v>82597</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1445</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>855041</v>
+        <v>855207</v>
       </c>
       <c r="R69" t="n">
-        <v>7477819</v>
+        <v>7477876</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7622,17 +7617,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7641,7 +7631,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7656,7 +7645,117 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY69" t="inlineStr">
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>124855535</v>
+      </c>
+      <c r="B70" t="n">
+        <v>83564</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>855041</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7477819</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF70" t="inlineStr"/>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr">
         <is>
           <t>Uppföljning bombmurkla 2025</t>
         </is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AY76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7761,6 +7761,612 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134414061</v>
+      </c>
+      <c r="B71" t="n">
+        <v>84195</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1445</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Bombmurkla</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Sarcosoma globosum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>855040</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7477820</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ej återfunnen. Fyndplatsen förstörd av skogsbruk.</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134119728</v>
+      </c>
+      <c r="B72" t="n">
+        <v>101287</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>8</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Röd trolldruva</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Actaea erythrocarpa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fisch.) Kom.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>855036</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7477819</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134119896</v>
+      </c>
+      <c r="B73" t="n">
+        <v>101287</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>8</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Röd trolldruva</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Actaea erythrocarpa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fisch.) Kom.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>855044</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7477826</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Mycket stora mängder röd trolldruva inom avverkat område.</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>134119735</v>
+      </c>
+      <c r="B74" t="n">
+        <v>101287</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>8</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Röd trolldruva</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Actaea erythrocarpa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Fisch.) Kom.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>855045</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7477816</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF74" t="inlineStr"/>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>134119727</v>
+      </c>
+      <c r="B75" t="n">
+        <v>101287</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>8</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Röd trolldruva</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Actaea erythrocarpa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fisch.) Kom.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>855057</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7477819</v>
+      </c>
+      <c r="S75" t="n">
+        <v>5</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>134119734</v>
+      </c>
+      <c r="B76" t="n">
+        <v>101287</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>8</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Röd trolldruva</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Actaea erythrocarpa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fisch.) Kom.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>855006</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7477817</v>
+      </c>
+      <c r="S76" t="n">
+        <v>5</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF76" t="inlineStr"/>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -7766,7 +7766,7 @@
         <v>134414061</v>
       </c>
       <c r="B71" t="n">
-        <v>84195</v>
+        <v>84202</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         <v>134119728</v>
       </c>
       <c r="B72" t="n">
-        <v>101287</v>
+        <v>101294</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>134119896</v>
       </c>
       <c r="B73" t="n">
-        <v>101287</v>
+        <v>101294</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8078,7 +8078,7 @@
         <v>134119735</v>
       </c>
       <c r="B74" t="n">
-        <v>101287</v>
+        <v>101294</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>134119727</v>
       </c>
       <c r="B75" t="n">
-        <v>101287</v>
+        <v>101294</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>134119734</v>
       </c>
       <c r="B76" t="n">
-        <v>101287</v>
+        <v>101294</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY76"/>
+  <dimension ref="A1:AY94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>115750492</v>
+        <v>134119727</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101301</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Röd trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Actaea erythrocarpa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fisch.) Kom.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kenttä-Kuusivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>855955</v>
+        <v>855057</v>
       </c>
       <c r="R2" t="n">
-        <v>7477657</v>
+        <v>7477819</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,33 +754,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115749944</v>
+        <v>134119728</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,41 +784,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>8</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Röd trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Actaea erythrocarpa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(Fisch.) Kom.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kenttä-Kuusivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>855955</v>
+        <v>855036</v>
       </c>
       <c r="R3" t="n">
-        <v>7477666</v>
+        <v>7477819</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +842,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,74 +856,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115750051</v>
+        <v>134119734</v>
       </c>
       <c r="B4" t="n">
-        <v>79464</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101301</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6456</v>
+        <v>8</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Röd trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Actaea erythrocarpa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fisch.) Kom.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kenttä-Kuusivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>856029</v>
+        <v>855006</v>
       </c>
       <c r="R4" t="n">
-        <v>7477661</v>
+        <v>7477817</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,12 +940,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,27 +961,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Viktoria Sturk, Marie Persson</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115749995</v>
+        <v>134119735</v>
       </c>
       <c r="B5" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101301</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1019,40 +984,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>8</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Röd trolldruva</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Actaea erythrocarpa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fisch.) Kom.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kenttä-Kuusivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>855963</v>
+        <v>855045</v>
       </c>
       <c r="R5" t="n">
-        <v>7477684</v>
+        <v>7477816</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,12 +1038,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-06</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1097,27 +1059,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marie Persson, Viktoria Sturk</t>
+          <t>Marie Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116387241</v>
+        <v>134119896</v>
       </c>
       <c r="B6" t="n">
-        <v>56482</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101301</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,37 +1082,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>8</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Röd trolldruva</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Actaea erythrocarpa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fisch.) Kom.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>856043</v>
+        <v>855044</v>
       </c>
       <c r="R6" t="n">
-        <v>7477593</v>
+        <v>7477826</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1179,12 +1136,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Mycket stora mängder röd trolldruva inom avverkat område.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1193,6 +1155,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,15 +1174,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116387282</v>
+        <v>117306757</v>
       </c>
       <c r="B7" t="n">
-        <v>78557</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1227,34 +1185,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>856023</v>
+        <v>855616</v>
       </c>
       <c r="R7" t="n">
-        <v>7477763</v>
+        <v>7478900</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1281,12 +1239,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1313,15 +1271,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116387284</v>
+        <v>119677117</v>
       </c>
       <c r="B8" t="n">
-        <v>78557</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,34 +1282,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>856073</v>
+        <v>855412</v>
       </c>
       <c r="R8" t="n">
-        <v>7477683</v>
+        <v>7478048</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,12 +1336,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1415,50 +1368,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116387229</v>
+        <v>117306813</v>
       </c>
       <c r="B9" t="n">
-        <v>57384</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92721</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>918</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tajgaskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Laurilia sulcata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Burt) Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>855993</v>
+        <v>855559</v>
       </c>
       <c r="R9" t="n">
-        <v>7477520</v>
+        <v>7478853</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,12 +1436,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1499,6 +1450,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1517,15 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116387285</v>
+        <v>119677121</v>
       </c>
       <c r="B10" t="n">
-        <v>78557</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1533,34 +1480,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>856016</v>
+        <v>855458</v>
       </c>
       <c r="R10" t="n">
-        <v>7477519</v>
+        <v>7478069</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,12 +1534,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1619,15 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116387246</v>
+        <v>119677122</v>
       </c>
       <c r="B11" t="n">
-        <v>90451</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1635,34 +1577,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>856062</v>
+        <v>855480</v>
       </c>
       <c r="R11" t="n">
-        <v>7477689</v>
+        <v>7478054</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,12 +1631,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,15 +1663,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116387283</v>
+        <v>117306742</v>
       </c>
       <c r="B12" t="n">
-        <v>78557</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,34 +1674,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>856067</v>
+        <v>855585</v>
       </c>
       <c r="R12" t="n">
-        <v>7477731</v>
+        <v>7478651</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,12 +1728,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1823,15 +1760,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116387240</v>
+        <v>117306743</v>
       </c>
       <c r="B13" t="n">
-        <v>56482</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,34 +1771,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>856038</v>
+        <v>855713</v>
       </c>
       <c r="R13" t="n">
-        <v>7477748</v>
+        <v>7478826</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,12 +1825,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1925,15 +1857,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116387281</v>
+        <v>117306744</v>
       </c>
       <c r="B14" t="n">
-        <v>78557</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1941,34 +1868,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>855999</v>
+        <v>855723</v>
       </c>
       <c r="R14" t="n">
-        <v>7477790</v>
+        <v>7478739</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,12 +1922,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2027,15 +1954,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>116387199</v>
+        <v>119677113</v>
       </c>
       <c r="B15" t="n">
-        <v>57277</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2043,34 +1965,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>856002</v>
+        <v>855429</v>
       </c>
       <c r="R15" t="n">
-        <v>7477486</v>
+        <v>7478011</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,12 +2019,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2129,15 +2051,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117306783</v>
+        <v>117306776</v>
       </c>
       <c r="B16" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2169,10 +2086,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>855611</v>
+        <v>855641</v>
       </c>
       <c r="R16" t="n">
-        <v>7478917</v>
+        <v>7478496</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2231,15 +2148,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117306764</v>
+        <v>117306777</v>
       </c>
       <c r="B17" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,21 +2159,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2271,10 +2183,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>855586</v>
+        <v>855633</v>
       </c>
       <c r="R17" t="n">
-        <v>7478904</v>
+        <v>7478544</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,12 +2248,7 @@
         <v>117306779</v>
       </c>
       <c r="B18" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2435,37 +2342,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117306749</v>
+        <v>117306780</v>
       </c>
       <c r="B19" t="n">
-        <v>79590</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2475,10 +2377,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>855666</v>
+        <v>855551</v>
       </c>
       <c r="R19" t="n">
-        <v>7478426</v>
+        <v>7478877</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2537,37 +2439,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117306747</v>
+        <v>117306781</v>
       </c>
       <c r="B20" t="n">
-        <v>56499</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2577,10 +2474,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>855565</v>
+        <v>855566</v>
       </c>
       <c r="R20" t="n">
-        <v>7478654</v>
+        <v>7478883</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2639,15 +2536,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117306801</v>
+        <v>117306782</v>
       </c>
       <c r="B21" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2679,10 +2571,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>855556</v>
+        <v>855585</v>
       </c>
       <c r="R21" t="n">
-        <v>7478643</v>
+        <v>7478885</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2741,15 +2633,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117306742</v>
+        <v>117306783</v>
       </c>
       <c r="B22" t="n">
-        <v>90499</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2757,21 +2644,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2781,10 +2668,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>855585</v>
+        <v>855611</v>
       </c>
       <c r="R22" t="n">
-        <v>7478651</v>
+        <v>7478917</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2843,15 +2730,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117306810</v>
+        <v>117306784</v>
       </c>
       <c r="B23" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2883,10 +2765,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>855631</v>
+        <v>855644</v>
       </c>
       <c r="R23" t="n">
-        <v>7478756</v>
+        <v>7479007</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2945,15 +2827,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117306809</v>
+        <v>117306785</v>
       </c>
       <c r="B24" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2985,10 +2862,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>855643</v>
+        <v>855646</v>
       </c>
       <c r="R24" t="n">
-        <v>7478745</v>
+        <v>7478946</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3047,37 +2924,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117306760</v>
+        <v>117306786</v>
       </c>
       <c r="B25" t="n">
-        <v>79597</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6464</v>
+        <v>1312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3087,10 +2959,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>855662</v>
+        <v>855712</v>
       </c>
       <c r="R25" t="n">
-        <v>7478500</v>
+        <v>7478804</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3149,15 +3021,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117306802</v>
+        <v>117306787</v>
       </c>
       <c r="B26" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3189,10 +3056,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>855575</v>
+        <v>855715</v>
       </c>
       <c r="R26" t="n">
-        <v>7478648</v>
+        <v>7478784</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3251,15 +3118,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117306784</v>
+        <v>117306788</v>
       </c>
       <c r="B27" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3291,10 +3153,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>855644</v>
+        <v>855715</v>
       </c>
       <c r="R27" t="n">
-        <v>7479007</v>
+        <v>7478747</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3353,15 +3215,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117306807</v>
+        <v>117306801</v>
       </c>
       <c r="B28" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3393,10 +3250,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>855611</v>
+        <v>855556</v>
       </c>
       <c r="R28" t="n">
-        <v>7478717</v>
+        <v>7478643</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3455,15 +3312,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117306750</v>
+        <v>117306802</v>
       </c>
       <c r="B29" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3471,21 +3323,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3495,10 +3347,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>855540</v>
+        <v>855575</v>
       </c>
       <c r="R29" t="n">
-        <v>7478638</v>
+        <v>7478648</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3557,15 +3409,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117306808</v>
+        <v>117306803</v>
       </c>
       <c r="B30" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3597,10 +3444,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>855646</v>
+        <v>855639</v>
       </c>
       <c r="R30" t="n">
-        <v>7478734</v>
+        <v>7478671</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3659,15 +3506,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117306757</v>
+        <v>117306804</v>
       </c>
       <c r="B31" t="n">
-        <v>90782</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3675,21 +3517,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3699,10 +3541,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>855616</v>
+        <v>855643</v>
       </c>
       <c r="R31" t="n">
-        <v>7478900</v>
+        <v>7478679</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3761,15 +3603,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117306763</v>
+        <v>117306805</v>
       </c>
       <c r="B32" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3777,21 +3614,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3801,10 +3638,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>855578</v>
+        <v>855643</v>
       </c>
       <c r="R32" t="n">
-        <v>7478882</v>
+        <v>7478701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3863,15 +3700,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117306752</v>
+        <v>117306807</v>
       </c>
       <c r="B33" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3879,21 +3711,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3903,10 +3735,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>855609</v>
+        <v>855611</v>
       </c>
       <c r="R33" t="n">
-        <v>7478989</v>
+        <v>7478717</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3965,15 +3797,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117306803</v>
+        <v>117306808</v>
       </c>
       <c r="B34" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4005,10 +3832,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>855639</v>
+        <v>855646</v>
       </c>
       <c r="R34" t="n">
-        <v>7478671</v>
+        <v>7478734</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4067,15 +3894,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117306781</v>
+        <v>117306809</v>
       </c>
       <c r="B35" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4107,10 +3929,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>855566</v>
+        <v>855643</v>
       </c>
       <c r="R35" t="n">
-        <v>7478883</v>
+        <v>7478745</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4169,15 +3991,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117306766</v>
+        <v>117306810</v>
       </c>
       <c r="B36" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4185,21 +4002,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4209,10 +4026,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>855598</v>
+        <v>855631</v>
       </c>
       <c r="R36" t="n">
-        <v>7478966</v>
+        <v>7478756</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4274,12 +4091,7 @@
         <v>117306811</v>
       </c>
       <c r="B37" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4373,15 +4185,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117306782</v>
+        <v>117306812</v>
       </c>
       <c r="B38" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4413,10 +4220,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>855585</v>
+        <v>855604</v>
       </c>
       <c r="R38" t="n">
-        <v>7478885</v>
+        <v>7478822</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4475,15 +4282,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117306785</v>
+        <v>119677133</v>
       </c>
       <c r="B39" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4511,14 +4313,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>855646</v>
+        <v>855497</v>
       </c>
       <c r="R39" t="n">
-        <v>7478946</v>
+        <v>7477946</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4545,12 +4347,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4577,15 +4379,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117306765</v>
+        <v>119677134</v>
       </c>
       <c r="B40" t="n">
-        <v>56491</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4593,34 +4390,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>102612</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>855580</v>
+        <v>855534</v>
       </c>
       <c r="R40" t="n">
-        <v>7478943</v>
+        <v>7477979</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4647,12 +4444,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4679,15 +4476,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117306751</v>
+        <v>119677135</v>
       </c>
       <c r="B41" t="n">
-        <v>57303</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4695,34 +4487,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>855550</v>
+        <v>855530</v>
       </c>
       <c r="R41" t="n">
-        <v>7478642</v>
+        <v>7478027</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4749,12 +4541,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4781,15 +4573,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117306780</v>
+        <v>119677146</v>
       </c>
       <c r="B42" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4817,14 +4604,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>855551</v>
+        <v>855547</v>
       </c>
       <c r="R42" t="n">
-        <v>7478877</v>
+        <v>7477962</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4851,12 +4638,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4883,15 +4670,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117306805</v>
+        <v>123699075</v>
       </c>
       <c r="B43" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4919,17 +4701,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>855643</v>
+        <v>855207</v>
       </c>
       <c r="R43" t="n">
-        <v>7478701</v>
+        <v>7477876</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4953,12 +4735,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4985,15 +4767,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117306777</v>
+        <v>124855493</v>
       </c>
       <c r="B44" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5021,14 +4798,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>855633</v>
+        <v>855343</v>
       </c>
       <c r="R44" t="n">
-        <v>7478544</v>
+        <v>7478075</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5055,12 +4832,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5087,50 +4864,52 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117306804</v>
+        <v>124855535</v>
       </c>
       <c r="B45" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84158</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>1445</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>(Schmidel:Fr.) Rehm</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>855643</v>
+        <v>855041</v>
       </c>
       <c r="R45" t="n">
-        <v>7478679</v>
+        <v>7477819</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5157,12 +4936,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5171,6 +4955,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5185,57 +4970,56 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY45" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117306746</v>
+        <v>134414061</v>
       </c>
       <c r="B46" t="n">
-        <v>56499</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>84209</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>1445</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bombmurkla</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sarcosoma globosum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schmidel:Fr.) Rehm</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>855666</v>
+        <v>855040</v>
       </c>
       <c r="R46" t="n">
-        <v>7478409</v>
+        <v>7477820</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5259,12 +5043,17 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ej återfunnen. Fyndplatsen förstörd av skogsbruk.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5273,6 +5062,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5287,19 +5077,18 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr"/>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Uppföljning bombmurkla</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117306770</v>
+        <v>118001743</v>
       </c>
       <c r="B47" t="n">
-        <v>90517</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5307,34 +5096,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>1588</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>855645</v>
+        <v>855635</v>
       </c>
       <c r="R47" t="n">
-        <v>7478615</v>
+        <v>7478691</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5375,6 +5164,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5393,50 +5183,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117306759</v>
+        <v>118001744</v>
       </c>
       <c r="B48" t="n">
-        <v>79597</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6464</v>
+        <v>1588</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>855688</v>
+        <v>855545</v>
       </c>
       <c r="R48" t="n">
-        <v>7478373</v>
+        <v>7478641</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5495,58 +5280,45 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117306758</v>
+        <v>118001745</v>
       </c>
       <c r="B49" t="n">
-        <v>56502</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92097</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>102613</v>
+        <v>1588</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855580</v>
+        <v>855552</v>
       </c>
       <c r="R49" t="n">
-        <v>7478885</v>
+        <v>7478635</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5581,17 +5353,13 @@
           <t>2024-05-24</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Blindtarmstöming</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5610,53 +5378,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117306776</v>
+        <v>134119897</v>
       </c>
       <c r="B50" t="n">
-        <v>82259</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96410</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>2812</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855641</v>
+        <v>855226</v>
       </c>
       <c r="R50" t="n">
-        <v>7478496</v>
+        <v>7477875</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5680,12 +5443,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Döende pga avverkning</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5694,6 +5462,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5712,37 +5481,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118001744</v>
+        <v>119677116</v>
       </c>
       <c r="B51" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91680</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1588</v>
+        <v>3215</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5752,10 +5516,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855545</v>
+        <v>855497</v>
       </c>
       <c r="R51" t="n">
-        <v>7478641</v>
+        <v>7477896</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5782,12 +5546,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5814,50 +5578,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118001743</v>
+        <v>117306815</v>
       </c>
       <c r="B52" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1588</v>
+        <v>4217</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855635</v>
+        <v>855559</v>
       </c>
       <c r="R52" t="n">
-        <v>7478691</v>
+        <v>7478853</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5898,7 +5657,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5917,37 +5675,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118001745</v>
+        <v>119677109</v>
       </c>
       <c r="B53" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1588</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5957,10 +5710,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855552</v>
+        <v>855492</v>
       </c>
       <c r="R53" t="n">
-        <v>7478635</v>
+        <v>7477928</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5987,12 +5740,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6001,7 +5754,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6020,37 +5772,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119677121</v>
+        <v>119677110</v>
       </c>
       <c r="B54" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6060,10 +5807,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>855458</v>
+        <v>855517</v>
       </c>
       <c r="R54" t="n">
-        <v>7478069</v>
+        <v>7477955</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6122,15 +5869,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119677116</v>
+        <v>119677111</v>
       </c>
       <c r="B55" t="n">
-        <v>90334</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6138,21 +5880,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>3215</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6162,10 +5904,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855497</v>
+        <v>855540</v>
       </c>
       <c r="R55" t="n">
-        <v>7477896</v>
+        <v>7478006</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6224,53 +5966,51 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119677108</v>
+        <v>115749995</v>
       </c>
       <c r="B56" t="n">
-        <v>58022</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103056</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kenttä-Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855446</v>
+        <v>855963</v>
       </c>
       <c r="R56" t="n">
-        <v>7478072</v>
+        <v>7477684</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6294,12 +6034,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6308,71 +6048,70 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119677111</v>
+        <v>115750366</v>
       </c>
       <c r="B57" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kenttä-Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>855540</v>
+        <v>855811</v>
       </c>
       <c r="R57" t="n">
-        <v>7478006</v>
+        <v>7477719</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6396,12 +6135,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6410,68 +6149,64 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119677134</v>
+        <v>116387281</v>
       </c>
       <c r="B58" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusinvaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>855534</v>
+        <v>855999</v>
       </c>
       <c r="R58" t="n">
-        <v>7477979</v>
+        <v>7477790</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6498,12 +6233,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6530,50 +6265,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119677109</v>
+        <v>116387282</v>
       </c>
       <c r="B59" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusinvaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>855492</v>
+        <v>856023</v>
       </c>
       <c r="R59" t="n">
-        <v>7477928</v>
+        <v>7477763</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6600,12 +6330,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6632,46 +6362,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119677118</v>
+        <v>116387283</v>
       </c>
       <c r="B60" t="n">
-        <v>96856</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221944</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusinvaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>855491</v>
+        <v>856067</v>
       </c>
       <c r="R60" t="n">
-        <v>7477890</v>
+        <v>7477731</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6698,12 +6427,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6712,7 +6441,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -6731,50 +6459,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119677122</v>
+        <v>116387284</v>
       </c>
       <c r="B61" t="n">
-        <v>90558</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusinvaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855480</v>
+        <v>856073</v>
       </c>
       <c r="R61" t="n">
-        <v>7478054</v>
+        <v>7477683</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6801,12 +6524,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6833,50 +6556,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119677113</v>
+        <v>116387285</v>
       </c>
       <c r="B62" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusinvaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855429</v>
+        <v>856016</v>
       </c>
       <c r="R62" t="n">
-        <v>7478011</v>
+        <v>7477519</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6903,12 +6621,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6935,50 +6653,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119677110</v>
+        <v>117306774</v>
       </c>
       <c r="B63" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855517</v>
+        <v>855718</v>
       </c>
       <c r="R63" t="n">
-        <v>7477955</v>
+        <v>7478812</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7005,12 +6718,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7037,50 +6750,45 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119677133</v>
+        <v>124855483</v>
       </c>
       <c r="B64" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>855497</v>
+        <v>855251</v>
       </c>
       <c r="R64" t="n">
-        <v>7477946</v>
+        <v>7478036</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7107,12 +6815,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7139,53 +6847,51 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119677123</v>
+        <v>115750051</v>
       </c>
       <c r="B65" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5432</v>
+        <v>6456</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kenttä-Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>855409</v>
+        <v>856029</v>
       </c>
       <c r="R65" t="n">
-        <v>7478024</v>
+        <v>7477661</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7209,12 +6915,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7223,68 +6929,64 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119677117</v>
+        <v>117306749</v>
       </c>
       <c r="B66" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>658</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855412</v>
+        <v>855666</v>
       </c>
       <c r="R66" t="n">
-        <v>7478048</v>
+        <v>7478426</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7311,12 +7013,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7343,50 +7045,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119677124</v>
+        <v>117306759</v>
       </c>
       <c r="B67" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>855474</v>
+        <v>855688</v>
       </c>
       <c r="R67" t="n">
-        <v>7478024</v>
+        <v>7478373</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7413,12 +7110,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7445,50 +7142,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119677135</v>
+        <v>117306760</v>
       </c>
       <c r="B68" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>855530</v>
+        <v>855662</v>
       </c>
       <c r="R68" t="n">
-        <v>7478027</v>
+        <v>7478500</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7515,12 +7207,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7547,53 +7239,52 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>123699075</v>
+        <v>115750492</v>
       </c>
       <c r="B69" t="n">
-        <v>82597</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kenttä-Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>855207</v>
+        <v>855955</v>
       </c>
       <c r="R69" t="n">
-        <v>7477876</v>
+        <v>7477657</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7617,12 +7308,17 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Hack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7637,64 +7333,57 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855535</v>
+        <v>117306750</v>
       </c>
       <c r="B70" t="n">
-        <v>83564</v>
+        <v>57950</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1445</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>855041</v>
+        <v>855540</v>
       </c>
       <c r="R70" t="n">
-        <v>7477819</v>
+        <v>7478638</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7721,17 +7410,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>2 meter  från hyggeskant bredvid bäck som svämar över på våren. Näringsrik berggrund indikeras också av ögonpyrola, kransmossa, knärot.  Då bäcken omges av hyggen på båda sidorna är lokalens utsikter för fortlevnad inte speciellt bra.  Biotopen har bestått av ca 200 årig grandominerad skog med inslag av gammal asp, sälg och björk. Dalgångslik svacka i sluttning mot närliggande myr.</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7740,7 +7424,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7755,56 +7438,52 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY70" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla 2025</t>
-        </is>
-      </c>
+      <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134414061</v>
+        <v>117306751</v>
       </c>
       <c r="B71" t="n">
-        <v>84202</v>
+        <v>57950</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1445</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bombmurkla</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sarcosoma globosum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Schmidel:Fr.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>855040</v>
+        <v>855550</v>
       </c>
       <c r="R71" t="n">
-        <v>7477820</v>
+        <v>7478642</v>
       </c>
       <c r="S71" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7828,17 +7507,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ej återfunnen. Fyndplatsen förstörd av skogsbruk.</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7847,7 +7521,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7862,60 +7535,52 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Uppföljning bombmurkla</t>
-        </is>
-      </c>
+      <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134119728</v>
+        <v>117306752</v>
       </c>
       <c r="B72" t="n">
-        <v>101294</v>
+        <v>57950</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>8</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Röd trolldruva</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Actaea erythrocarpa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fisch.) Kom.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>855036</v>
+        <v>855609</v>
       </c>
       <c r="R72" t="n">
-        <v>7477819</v>
+        <v>7478989</v>
       </c>
       <c r="S72" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7939,12 +7604,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7953,7 +7618,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7972,10 +7636,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134119896</v>
+        <v>115749944</v>
       </c>
       <c r="B73" t="n">
-        <v>101294</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7983,37 +7647,41 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>8</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Röd trolldruva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Actaea erythrocarpa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fisch.) Kom.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Kenttä-Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855044</v>
+        <v>855955</v>
       </c>
       <c r="R73" t="n">
-        <v>7477826</v>
+        <v>7477666</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8037,17 +7705,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Mycket stora mängder röd trolldruva inom avverkat område.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8056,29 +7724,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134119735</v>
+        <v>115750410</v>
       </c>
       <c r="B74" t="n">
-        <v>101294</v>
+        <v>57953</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8086,37 +7753,41 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>8</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Röd trolldruva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Actaea erythrocarpa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fisch.) Kom.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Kenttä-Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>855045</v>
+        <v>855815</v>
       </c>
       <c r="R74" t="n">
-        <v>7477816</v>
+        <v>7477721</v>
       </c>
       <c r="S74" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8140,12 +7811,17 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8154,29 +7830,28 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134119727</v>
+        <v>115750460</v>
       </c>
       <c r="B75" t="n">
-        <v>101294</v>
+        <v>57953</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8184,37 +7859,41 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>8</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Röd trolldruva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Actaea erythrocarpa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fisch.) Kom.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Kenttä-Kuusivaara, Nb</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>855057</v>
+        <v>855843</v>
       </c>
       <c r="R75" t="n">
-        <v>7477819</v>
+        <v>7477634</v>
       </c>
       <c r="S75" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8238,12 +7917,17 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-06</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-06</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8252,29 +7936,28 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marie Karlsson</t>
+          <t>Viktoria Sturk, Marie Persson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134119734</v>
+        <v>116387199</v>
       </c>
       <c r="B76" t="n">
-        <v>101294</v>
+        <v>57953</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8282,37 +7965,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>8</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Röd trolldruva</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Actaea erythrocarpa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fisch.) Kom.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Kuusinvaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855006</v>
+        <v>856002</v>
       </c>
       <c r="R76" t="n">
-        <v>7477817</v>
+        <v>7477486</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8336,12 +8019,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8350,7 +8033,6 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8366,6 +8048,1777 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>116387240</v>
+      </c>
+      <c r="B77" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kuusinvaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>856038</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7477748</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>116387241</v>
+      </c>
+      <c r="B78" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kuusinvaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>856043</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7477593</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>117306763</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>855578</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7478882</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>117306764</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>855586</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7478904</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>117306765</v>
+      </c>
+      <c r="B81" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>855580</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7478943</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>117306766</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kuusivaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>855598</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7478966</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-05-24</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>116387229</v>
+      </c>
+      <c r="B83" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Kuusinvaaranoja, Nb</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>855993</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7477520</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-04-22</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>119677108</v>
+      </c>
+      <c r="B84" t="n">
+        <v>58656</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Torinen, Nb</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>855446</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7478072</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134119723</v>
+      </c>
+      <c r="B85" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>854988</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7477812</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>124855356</v>
+      </c>
+      <c r="B86" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>855004</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7477822</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF86" t="inlineStr"/>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>124855357</v>
+      </c>
+      <c r="B87" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>855032</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7477845</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="inlineStr"/>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>124855360</v>
+      </c>
+      <c r="B88" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>854994</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7477840</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>124855411</v>
+      </c>
+      <c r="B89" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>855100</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7477871</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>124855425</v>
+      </c>
+      <c r="B90" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>855037</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7477854</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>124855426</v>
+      </c>
+      <c r="B91" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>855070</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7477858</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>119677118</v>
+      </c>
+      <c r="B92" t="n">
+        <v>97977</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Torinen, Nb</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>855491</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7477890</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-09-07</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>134119807</v>
+      </c>
+      <c r="B93" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>855268</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7477876</v>
+      </c>
+      <c r="S93" t="n">
+        <v>5</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>134119808</v>
+      </c>
+      <c r="B94" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>855303</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7477930</v>
+      </c>
+      <c r="S94" t="n">
+        <v>5</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY94"/>
+  <dimension ref="A1:AY96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8051,27 +8051,27 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>116387240</v>
+        <v>134635859</v>
       </c>
       <c r="B77" t="n">
-        <v>57132</v>
+        <v>57975</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -8080,19 +8080,23 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>856038</v>
+        <v>855231</v>
       </c>
       <c r="R77" t="n">
-        <v>7477748</v>
+        <v>7477868</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8116,12 +8120,17 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8148,27 +8157,27 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>116387241</v>
+        <v>134635860</v>
       </c>
       <c r="B78" t="n">
-        <v>57132</v>
+        <v>57975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -8177,19 +8186,23 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>856043</v>
+        <v>855220</v>
       </c>
       <c r="R78" t="n">
-        <v>7477593</v>
+        <v>7477866</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8213,12 +8226,17 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8245,7 +8263,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>117306763</v>
+        <v>116387240</v>
       </c>
       <c r="B79" t="n">
         <v>57132</v>
@@ -8276,14 +8294,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Kuusinvaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855578</v>
+        <v>856038</v>
       </c>
       <c r="R79" t="n">
-        <v>7478882</v>
+        <v>7477748</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8310,12 +8328,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8342,7 +8360,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>117306764</v>
+        <v>116387241</v>
       </c>
       <c r="B80" t="n">
         <v>57132</v>
@@ -8373,14 +8391,14 @@
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kuusivaaranoja, Nb</t>
+          <t>Kuusinvaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855586</v>
+        <v>856043</v>
       </c>
       <c r="R80" t="n">
-        <v>7478904</v>
+        <v>7477593</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8407,12 +8425,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-05-24</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8439,7 +8457,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>117306765</v>
+        <v>117306763</v>
       </c>
       <c r="B81" t="n">
         <v>57132</v>
@@ -8474,10 +8492,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>855580</v>
+        <v>855578</v>
       </c>
       <c r="R81" t="n">
-        <v>7478943</v>
+        <v>7478882</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8536,7 +8554,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>117306766</v>
+        <v>117306764</v>
       </c>
       <c r="B82" t="n">
         <v>57132</v>
@@ -8571,10 +8589,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855598</v>
+        <v>855586</v>
       </c>
       <c r="R82" t="n">
-        <v>7478966</v>
+        <v>7478904</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8633,27 +8651,27 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>116387229</v>
+        <v>117306765</v>
       </c>
       <c r="B83" t="n">
-        <v>58057</v>
+        <v>57132</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>103031</v>
+        <v>102612</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8664,14 +8682,14 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Kuusinvaaranoja, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>855993</v>
+        <v>855580</v>
       </c>
       <c r="R83" t="n">
-        <v>7477520</v>
+        <v>7478943</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8698,12 +8716,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-04-22</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8730,10 +8748,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119677108</v>
+        <v>117306766</v>
       </c>
       <c r="B84" t="n">
-        <v>58656</v>
+        <v>57132</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8741,34 +8759,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>103056</v>
+        <v>102612</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Kuusivaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855446</v>
+        <v>855598</v>
       </c>
       <c r="R84" t="n">
-        <v>7478072</v>
+        <v>7478966</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8795,12 +8813,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2024-05-24</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8827,48 +8845,48 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134119723</v>
+        <v>116387229</v>
       </c>
       <c r="B85" t="n">
-        <v>58839</v>
+        <v>58057</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>208249</v>
+        <v>103031</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Kuusinvaaranoja, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854988</v>
+        <v>855993</v>
       </c>
       <c r="R85" t="n">
-        <v>7477812</v>
+        <v>7477520</v>
       </c>
       <c r="S85" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8892,12 +8910,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-04-22</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8924,45 +8942,45 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>124855356</v>
+        <v>119677108</v>
       </c>
       <c r="B86" t="n">
-        <v>99118</v>
+        <v>58656</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>220787</v>
+        <v>103056</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>855004</v>
+        <v>855446</v>
       </c>
       <c r="R86" t="n">
-        <v>7477822</v>
+        <v>7478072</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8989,17 +9007,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9008,7 +9021,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -9027,52 +9039,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855357</v>
+        <v>134119723</v>
       </c>
       <c r="B87" t="n">
-        <v>99118</v>
+        <v>58839</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>208249</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>855032</v>
+        <v>854988</v>
       </c>
       <c r="R87" t="n">
-        <v>7477845</v>
+        <v>7477812</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9096,17 +9104,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9115,7 +9118,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9134,7 +9136,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855360</v>
+        <v>124855356</v>
       </c>
       <c r="B88" t="n">
         <v>99118</v>
@@ -9169,10 +9171,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854994</v>
+        <v>855004</v>
       </c>
       <c r="R88" t="n">
-        <v>7477840</v>
+        <v>7477822</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9237,7 +9239,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>124855411</v>
+        <v>124855357</v>
       </c>
       <c r="B89" t="n">
         <v>99118</v>
@@ -9265,17 +9267,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855100</v>
+        <v>855032</v>
       </c>
       <c r="R89" t="n">
-        <v>7477871</v>
+        <v>7477845</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9340,7 +9346,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124855425</v>
+        <v>124855360</v>
       </c>
       <c r="B90" t="n">
         <v>99118</v>
@@ -9371,14 +9377,14 @@
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>855037</v>
+        <v>854994</v>
       </c>
       <c r="R90" t="n">
-        <v>7477854</v>
+        <v>7477840</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9413,12 +9419,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -9437,7 +9449,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>124855426</v>
+        <v>124855411</v>
       </c>
       <c r="B91" t="n">
         <v>99118</v>
@@ -9472,10 +9484,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>855070</v>
+        <v>855100</v>
       </c>
       <c r="R91" t="n">
-        <v>7477858</v>
+        <v>7477871</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9510,12 +9522,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
       <c r="AE91" t="b">
         <v>0</v>
       </c>
+      <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
       </c>
@@ -9534,41 +9552,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119677118</v>
+        <v>124855425</v>
       </c>
       <c r="B92" t="n">
-        <v>97977</v>
+        <v>99118</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>221944</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855491</v>
+        <v>855037</v>
       </c>
       <c r="R92" t="n">
-        <v>7477890</v>
+        <v>7477854</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9595,12 +9617,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2024-09-07</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -9609,7 +9631,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -9628,48 +9649,48 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134119807</v>
+        <v>124855426</v>
       </c>
       <c r="B93" t="n">
-        <v>99001</v>
+        <v>99118</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>223049</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>855268</v>
+        <v>855070</v>
       </c>
       <c r="R93" t="n">
-        <v>7477876</v>
+        <v>7477858</v>
       </c>
       <c r="S93" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -9693,12 +9714,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -9725,10 +9746,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134119808</v>
+        <v>119677118</v>
       </c>
       <c r="B94" t="n">
-        <v>99001</v>
+        <v>97977</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9736,37 +9757,33 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>223049</v>
+        <v>221944</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>855303</v>
+        <v>855491</v>
       </c>
       <c r="R94" t="n">
-        <v>7477930</v>
+        <v>7477890</v>
       </c>
       <c r="S94" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -9790,12 +9807,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-09-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -9804,6 +9821,7 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
+      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -9819,6 +9837,200 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>134119807</v>
+      </c>
+      <c r="B95" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>855268</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7477876</v>
+      </c>
+      <c r="S95" t="n">
+        <v>5</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>134119808</v>
+      </c>
+      <c r="B96" t="n">
+        <v>99001</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>855303</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7477930</v>
+      </c>
+      <c r="S96" t="n">
+        <v>5</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7325-2024 artfynd.xlsx
+++ b/artfynd/A 7325-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119727</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119728</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -970,6 +985,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119734</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119735</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1171,6 +1196,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119896</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1268,6 +1298,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306757</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1365,6 +1400,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677117</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1466,6 +1506,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306813</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1563,6 +1608,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677121</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1660,6 +1710,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677122</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1757,6 +1812,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306742</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1854,6 +1914,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306743</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1951,6 +2016,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306744</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2048,6 +2118,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677113</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2145,6 +2220,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306776</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2242,6 +2322,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306777</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2339,6 +2424,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306779</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2436,6 +2526,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306780</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2533,6 +2628,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306781</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2630,6 +2730,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306782</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2727,6 +2832,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306783</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2824,6 +2934,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306784</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2921,6 +3036,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306785</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3018,6 +3138,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306786</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3115,6 +3240,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306787</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3212,6 +3342,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306788</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3309,6 +3444,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306801</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3406,6 +3546,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306802</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3503,6 +3648,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306803</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3600,6 +3750,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306804</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3697,6 +3852,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306805</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3794,6 +3954,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306807</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3891,6 +4056,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306808</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3988,6 +4158,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306809</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4085,6 +4260,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306810</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4182,6 +4362,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306811</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4279,6 +4464,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306812</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4376,6 +4566,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677133</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4473,6 +4668,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677134</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4570,6 +4770,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677135</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4667,6 +4872,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677146</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4764,6 +4974,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123699075</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4861,6 +5076,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855493</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4975,6 +5195,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855535</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5082,6 +5307,11 @@
           <t>Uppföljning bombmurkla</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134414061</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5180,6 +5410,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118001743</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5277,6 +5512,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118001744</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5375,6 +5615,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118001745</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5478,6 +5723,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119897</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5575,6 +5825,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677116</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5672,6 +5927,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306815</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5769,6 +6029,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677109</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5866,6 +6131,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677110</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5963,6 +6233,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677111</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6064,6 +6339,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115749995</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6165,6 +6445,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115750366</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6262,6 +6547,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387281</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6359,6 +6649,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387282</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6456,6 +6751,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387283</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6553,6 +6853,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387284</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6650,6 +6955,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387285</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6747,6 +7057,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306774</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6844,6 +7159,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855483</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6945,6 +7265,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115750051</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7042,6 +7367,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306749</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7139,6 +7469,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306759</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7236,6 +7571,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306760</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7342,6 +7682,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115750492</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7439,6 +7784,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306750</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7536,6 +7886,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306751</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7633,6 +7988,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306752</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7739,6 +8099,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115749944</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7845,6 +8210,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115750410</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7951,6 +8321,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115750460</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8048,6 +8423,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387199</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8154,6 +8534,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134635859</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8260,6 +8645,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134635860</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8357,6 +8747,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387240</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8454,6 +8849,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387241</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8551,6 +8951,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306763</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8648,6 +9053,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306764</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8745,6 +9155,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306765</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8842,6 +9257,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117306766</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8939,6 +9359,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116387229</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9036,6 +9461,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677108</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9133,6 +9563,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119723</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9236,6 +9671,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855356</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9343,6 +9783,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855357</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9446,6 +9891,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855360</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9549,6 +9999,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855411</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9646,6 +10101,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855425</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9743,6 +10203,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855426</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9837,6 +10302,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119677118</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9934,6 +10404,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119807</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10031,8 +10506,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119808</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>